--- a/data/seizure_stage.xlsx
+++ b/data/seizure_stage.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="187">
   <si>
     <t>Stage</t>
   </si>
@@ -360,12 +360,6 @@
     <t>12:25 - 12:35</t>
   </si>
   <si>
-    <t>13:35 - 13:46</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>19:12 - 19:35</t>
   </si>
   <si>
@@ -493,6 +487,99 @@
   </si>
   <si>
     <t>54:43 - 54:46</t>
+  </si>
+  <si>
+    <t>54:53 - 54:57</t>
+  </si>
+  <si>
+    <t>6:03 - 6:33</t>
+  </si>
+  <si>
+    <t>6:57 - 6:59</t>
+  </si>
+  <si>
+    <t>7:15 - 7:17</t>
+  </si>
+  <si>
+    <t>14:44 - 15:23</t>
+  </si>
+  <si>
+    <t>15:29 - 15:59</t>
+  </si>
+  <si>
+    <t>16:07 - 16:15</t>
+  </si>
+  <si>
+    <t>16:43 - 17:17</t>
+  </si>
+  <si>
+    <t>18:04 - 18:51</t>
+  </si>
+  <si>
+    <t>18:56 - 19:11</t>
+  </si>
+  <si>
+    <t>20:10 - 20:12</t>
+  </si>
+  <si>
+    <t>23:49 - 24:50</t>
+  </si>
+  <si>
+    <t>28:45 - 29:42</t>
+  </si>
+  <si>
+    <t>30:03 - 30:22</t>
+  </si>
+  <si>
+    <t>34:28 - 34:35</t>
+  </si>
+  <si>
+    <t>34:41 - 34:47</t>
+  </si>
+  <si>
+    <t>35:43 - 35:57</t>
+  </si>
+  <si>
+    <t>36:31 - 38:08</t>
+  </si>
+  <si>
+    <t>38:17 - 38:48</t>
+  </si>
+  <si>
+    <t>40:06 - 40:29</t>
+  </si>
+  <si>
+    <t>40:38 - 44:10</t>
+  </si>
+  <si>
+    <t>44:37 - 45:44</t>
+  </si>
+  <si>
+    <t>45:50 - 46:30</t>
+  </si>
+  <si>
+    <t>46:35 - 47:15</t>
+  </si>
+  <si>
+    <t>47:24 - 47:26</t>
+  </si>
+  <si>
+    <t>47:42 - 47:56</t>
+  </si>
+  <si>
+    <t>48:40 - 50:02</t>
+  </si>
+  <si>
+    <t>50:06 - 52:09</t>
+  </si>
+  <si>
+    <t>52:21 - 55:06</t>
+  </si>
+  <si>
+    <t>55:14 - 57:29</t>
+  </si>
+  <si>
+    <t>58:29 - 1:00:03</t>
   </si>
 </sst>
 </file>
@@ -11572,35 +11659,32 @@
       <c r="A3" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="3">
-        <v>2.0</v>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>117</v>
+      <c r="C5" s="6" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -11608,15 +11692,15 @@
         <v>119</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>120</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -11624,36 +11708,36 @@
         <v>122</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>123</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>33</v>
@@ -11661,23 +11745,23 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>25</v>
@@ -11685,7 +11769,7 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>25</v>
@@ -11693,43 +11777,38 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="C22" s="3"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="C23" s="3"/>
@@ -14661,9 +14740,6 @@
     </row>
     <row r="999" ht="15.75" customHeight="1">
       <c r="C999" s="3"/>
-    </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="C1000" s="3"/>
     </row>
   </sheetData>
   <printOptions/>
@@ -14696,7 +14772,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C2" s="7">
         <v>45659.0</v>
@@ -14704,7 +14780,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C3" s="7">
         <v>45691.0</v>
@@ -14712,7 +14788,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C4" s="1">
         <v>3.0</v>
@@ -14720,7 +14796,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C5" s="7">
         <v>45691.0</v>
@@ -14728,7 +14804,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C6" s="7">
         <v>45662.0</v>
@@ -14736,7 +14812,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C7" s="7">
         <v>45662.0</v>
@@ -15766,7 +15842,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C2" s="1">
         <v>2.0</v>
@@ -15774,7 +15850,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C3" s="1">
         <v>2.0</v>
@@ -15782,7 +15858,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C4" s="1">
         <v>2.0</v>
@@ -15790,7 +15866,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C5" s="7">
         <v>45660.0</v>
@@ -15798,7 +15874,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C6" s="7">
         <v>45659.0</v>
@@ -15806,7 +15882,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C7" s="1">
         <v>1.0</v>
@@ -15814,7 +15890,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C8" s="1">
         <v>1.0</v>
@@ -15822,7 +15898,7 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C9" s="1">
         <v>2.0</v>
@@ -15830,7 +15906,7 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C10" s="1">
         <v>2.0</v>
@@ -15838,7 +15914,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C11" s="1">
         <v>2.0</v>
@@ -15846,7 +15922,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C12" s="7">
         <v>45659.0</v>
@@ -15854,7 +15930,7 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C13" s="1">
         <v>2.0</v>
@@ -15862,7 +15938,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C14" s="1">
         <v>2.0</v>
@@ -15870,7 +15946,7 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C15" s="1">
         <v>2.0</v>
@@ -15878,13 +15954,20 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C16" s="1">
         <v>2.0</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
     <row r="20" ht="15.75" customHeight="1"/>
@@ -16883,7 +16966,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="10.56"/>
+    <col customWidth="1" min="1" max="1" width="12.0"/>
+    <col customWidth="1" min="2" max="26" width="10.56"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -16897,36 +16981,246 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1"/>
-    <row r="3" ht="15.75" customHeight="1"/>
-    <row r="4" ht="15.75" customHeight="1"/>
-    <row r="5" ht="15.75" customHeight="1"/>
-    <row r="6" ht="15.75" customHeight="1"/>
-    <row r="7" ht="15.75" customHeight="1"/>
-    <row r="8" ht="15.75" customHeight="1"/>
-    <row r="9" ht="15.75" customHeight="1"/>
-    <row r="10" ht="15.75" customHeight="1"/>
-    <row r="11" ht="15.75" customHeight="1"/>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="7">
+        <v>45660.0</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="7">
+        <v>45660.0</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="7">
+        <v>45659.0</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45659.0</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="7">
+        <v>45659.0</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="7">
+        <v>45693.0</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" s="7">
+        <v>45659.0</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" s="7">
+        <v>45659.0</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C20" s="7">
+        <v>45660.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="7">
+        <v>45660.0</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="7">
+        <v>45693.0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="7">
+        <v>45660.0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="7">
+        <v>45693.0</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C29" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C30" s="7">
+        <v>45693.0</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C31" s="7">
+        <v>45693.0</v>
+      </c>
+    </row>
     <row r="32" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>

--- a/data/seizure_stage.xlsx
+++ b/data/seizure_stage.xlsx
@@ -12,6 +12,22 @@
     <sheet state="visible" name="112625M1_B" sheetId="7" r:id="rId10"/>
     <sheet state="visible" name="112625M2" sheetId="8" r:id="rId11"/>
     <sheet state="visible" name="112625M2_B" sheetId="9" r:id="rId12"/>
+    <sheet state="visible" name="120725M1" sheetId="10" r:id="rId13"/>
+    <sheet state="visible" name="120725M1_B" sheetId="11" r:id="rId14"/>
+    <sheet state="visible" name="120725F1" sheetId="12" r:id="rId15"/>
+    <sheet state="visible" name="120725F1_B" sheetId="13" r:id="rId16"/>
+    <sheet state="visible" name="120725F2" sheetId="14" r:id="rId17"/>
+    <sheet state="visible" name="120725F2_B" sheetId="15" r:id="rId18"/>
+    <sheet state="visible" name="121125F1" sheetId="16" r:id="rId19"/>
+    <sheet state="visible" name="121125F1_B" sheetId="17" r:id="rId20"/>
+    <sheet state="visible" name="121125M1" sheetId="18" r:id="rId21"/>
+    <sheet state="visible" name="121125M1_B" sheetId="19" r:id="rId22"/>
+    <sheet state="visible" name="121125M2" sheetId="20" r:id="rId23"/>
+    <sheet state="visible" name="121125M2_B" sheetId="21" r:id="rId24"/>
+    <sheet state="visible" name="121225F1" sheetId="22" r:id="rId25"/>
+    <sheet state="visible" name="121225F1_B" sheetId="23" r:id="rId26"/>
+    <sheet state="visible" name="121225F2" sheetId="24" r:id="rId27"/>
+    <sheet state="visible" name="121225F2_B" sheetId="25" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -19,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="516">
   <si>
     <t>Stage</t>
   </si>
@@ -580,6 +596,993 @@
   </si>
   <si>
     <t>58:29 - 1:00:03</t>
+  </si>
+  <si>
+    <t>18:54 - 19:01</t>
+  </si>
+  <si>
+    <t>23:28 - 23:34</t>
+  </si>
+  <si>
+    <t>24:57 - 25:00</t>
+  </si>
+  <si>
+    <t>25:07 - 25:09</t>
+  </si>
+  <si>
+    <t>26:14 - 26:32</t>
+  </si>
+  <si>
+    <t>26:38 - 26:44</t>
+  </si>
+  <si>
+    <t>26:48 - 26:49</t>
+  </si>
+  <si>
+    <t>26:53 - 26:58</t>
+  </si>
+  <si>
+    <t>27:24 - 27:28</t>
+  </si>
+  <si>
+    <t>28:00 - 28:30</t>
+  </si>
+  <si>
+    <t>29:21 - 29:24</t>
+  </si>
+  <si>
+    <t>29:36 - 29:38</t>
+  </si>
+  <si>
+    <t>31:38 - 31:43</t>
+  </si>
+  <si>
+    <t>31:46 - 31:55</t>
+  </si>
+  <si>
+    <t>32:00 - 32:08</t>
+  </si>
+  <si>
+    <t>33:34 - 33:37</t>
+  </si>
+  <si>
+    <t>33:54 - 33:56</t>
+  </si>
+  <si>
+    <t>36:36 - 36:38</t>
+  </si>
+  <si>
+    <t>37:33 - 37:35</t>
+  </si>
+  <si>
+    <t>39:08 - 39:12</t>
+  </si>
+  <si>
+    <t>41:00 - 41:10</t>
+  </si>
+  <si>
+    <t>43:00 - 43:04</t>
+  </si>
+  <si>
+    <t>43:55 - 44:17</t>
+  </si>
+  <si>
+    <t>44:41 - 44:44</t>
+  </si>
+  <si>
+    <t>44:50 - 44:52</t>
+  </si>
+  <si>
+    <t>46:33 - 36:42</t>
+  </si>
+  <si>
+    <t>47:20 - 47:26</t>
+  </si>
+  <si>
+    <t>48:21 - 48:26</t>
+  </si>
+  <si>
+    <t>50:33 - 50:35</t>
+  </si>
+  <si>
+    <t>51:12 - 51:16</t>
+  </si>
+  <si>
+    <t>51:58 - 52:24</t>
+  </si>
+  <si>
+    <t>52:56 - 52:57</t>
+  </si>
+  <si>
+    <t>53:09 - 53:10</t>
+  </si>
+  <si>
+    <t>54:37 - 54:55</t>
+  </si>
+  <si>
+    <t>54:58 - 55:01</t>
+  </si>
+  <si>
+    <t>55:05 - 55:16</t>
+  </si>
+  <si>
+    <t>55:26 - 55:28</t>
+  </si>
+  <si>
+    <t>55:40 - 55:44</t>
+  </si>
+  <si>
+    <t>55:55 - 55:56</t>
+  </si>
+  <si>
+    <t>56:07 - 56:11</t>
+  </si>
+  <si>
+    <t>56:13 - 56:16</t>
+  </si>
+  <si>
+    <t>56:27 - 56:32</t>
+  </si>
+  <si>
+    <t>57:55 - 57:59</t>
+  </si>
+  <si>
+    <t>58:39 - 58:55</t>
+  </si>
+  <si>
+    <t>59:28 - 59:36</t>
+  </si>
+  <si>
+    <t>1:51 - 1:55</t>
+  </si>
+  <si>
+    <t>2:08 - 2:10</t>
+  </si>
+  <si>
+    <t>3:12 - 3:35</t>
+  </si>
+  <si>
+    <t>8:37 - 8:55</t>
+  </si>
+  <si>
+    <t>9:45 - 9:47</t>
+  </si>
+  <si>
+    <t>13:23 - 14:50</t>
+  </si>
+  <si>
+    <t>16:30 - 17:21</t>
+  </si>
+  <si>
+    <t>17:37 - 20:42</t>
+  </si>
+  <si>
+    <t>20:59 - 21:06</t>
+  </si>
+  <si>
+    <t>21:42 - 21:54</t>
+  </si>
+  <si>
+    <t>23:12 - 23:20</t>
+  </si>
+  <si>
+    <t>24:00 - 24:05</t>
+  </si>
+  <si>
+    <t>25:43 - 25:45</t>
+  </si>
+  <si>
+    <t>26:15 - 26:28</t>
+  </si>
+  <si>
+    <t>26:44 - 26:48</t>
+  </si>
+  <si>
+    <t>26:52 - 27:25</t>
+  </si>
+  <si>
+    <t>27:36 - 27:46</t>
+  </si>
+  <si>
+    <t>27:52 - 27:53</t>
+  </si>
+  <si>
+    <t>28:00 - 28:09</t>
+  </si>
+  <si>
+    <t>29:24 - 29:41</t>
+  </si>
+  <si>
+    <t>30:16 - 30:34</t>
+  </si>
+  <si>
+    <t>30:38 - 30:40</t>
+  </si>
+  <si>
+    <t>30:46 - 30:56</t>
+  </si>
+  <si>
+    <t>31:00 - 31:23</t>
+  </si>
+  <si>
+    <t>31:31 - 31:50</t>
+  </si>
+  <si>
+    <t>33:31 - 33:36</t>
+  </si>
+  <si>
+    <t>34:45 - 34:51</t>
+  </si>
+  <si>
+    <t>35:35 - 35:49</t>
+  </si>
+  <si>
+    <t>35:53 - 36:34</t>
+  </si>
+  <si>
+    <t>36:50 - 37:06</t>
+  </si>
+  <si>
+    <t>37:51 - 37:59</t>
+  </si>
+  <si>
+    <t>38:05 - 38:55</t>
+  </si>
+  <si>
+    <t>39:09 - 39:22</t>
+  </si>
+  <si>
+    <t>40:09 - 40:36</t>
+  </si>
+  <si>
+    <t>40:48 - 41:07</t>
+  </si>
+  <si>
+    <t>41:14 - 41:39</t>
+  </si>
+  <si>
+    <t>41:45 - 42:19</t>
+  </si>
+  <si>
+    <t>43:07 - 44:57</t>
+  </si>
+  <si>
+    <t>45:04 - 45:15</t>
+  </si>
+  <si>
+    <t>45:30 - 45:43</t>
+  </si>
+  <si>
+    <t>46:05 - 46:19</t>
+  </si>
+  <si>
+    <t>46:22 - 46:24</t>
+  </si>
+  <si>
+    <t>46:39 - 47:19</t>
+  </si>
+  <si>
+    <t>47:37 - 47:48</t>
+  </si>
+  <si>
+    <t>47:52 - 47:55</t>
+  </si>
+  <si>
+    <t>48:29 - 48:35</t>
+  </si>
+  <si>
+    <t>48:43 - 50:15</t>
+  </si>
+  <si>
+    <t>50:21 - 50:31</t>
+  </si>
+  <si>
+    <t>50:48 - 50:56</t>
+  </si>
+  <si>
+    <t>51:21 - 51:31</t>
+  </si>
+  <si>
+    <t>51:51 - 52:13</t>
+  </si>
+  <si>
+    <t>52:18 - 53:49</t>
+  </si>
+  <si>
+    <t>54:20 - 54:48</t>
+  </si>
+  <si>
+    <t>55:42 - 55:45</t>
+  </si>
+  <si>
+    <t>55:52 - 55:55</t>
+  </si>
+  <si>
+    <t>56:02 - 56:08</t>
+  </si>
+  <si>
+    <t>56:14 - 56:16</t>
+  </si>
+  <si>
+    <t>57:15 - 57:24</t>
+  </si>
+  <si>
+    <t>57:42 - 57:50</t>
+  </si>
+  <si>
+    <t>58:03 - 58:10</t>
+  </si>
+  <si>
+    <t>58:29 - 59:21</t>
+  </si>
+  <si>
+    <t>59:31 - 59:41</t>
+  </si>
+  <si>
+    <t>59:53 - 1:00:01</t>
+  </si>
+  <si>
+    <t>0:55 - 0:58</t>
+  </si>
+  <si>
+    <t>5:22 - 5:29</t>
+  </si>
+  <si>
+    <t>6:51 - 6:55</t>
+  </si>
+  <si>
+    <t>7:50 - 8:03</t>
+  </si>
+  <si>
+    <t>11:16 - 11:19</t>
+  </si>
+  <si>
+    <t>13:13 - 13:18</t>
+  </si>
+  <si>
+    <t>13:25 - 13:27</t>
+  </si>
+  <si>
+    <t>13:38 - 13:41</t>
+  </si>
+  <si>
+    <t>17:44 - 17:53</t>
+  </si>
+  <si>
+    <t>18:17 - 18:23</t>
+  </si>
+  <si>
+    <t>0:00 - 0:41</t>
+  </si>
+  <si>
+    <t>0:54 - 1:00</t>
+  </si>
+  <si>
+    <t>1:16 - 1:44</t>
+  </si>
+  <si>
+    <t>2:55 - 3:00</t>
+  </si>
+  <si>
+    <t>3:09 - 3:13</t>
+  </si>
+  <si>
+    <t>6:53 - 7:35</t>
+  </si>
+  <si>
+    <t>8:21 - 8:54</t>
+  </si>
+  <si>
+    <t>9:38 - 9:44</t>
+  </si>
+  <si>
+    <t>10:27 - 10:30</t>
+  </si>
+  <si>
+    <t>11:06 - 11:10</t>
+  </si>
+  <si>
+    <t>11:55 - 11:58</t>
+  </si>
+  <si>
+    <t>12:58 - 14:10</t>
+  </si>
+  <si>
+    <t>15:39 - 16:16</t>
+  </si>
+  <si>
+    <t>16:36 - 19:13</t>
+  </si>
+  <si>
+    <t>21:09 - 21:13</t>
+  </si>
+  <si>
+    <t>25:34 - 25:37</t>
+  </si>
+  <si>
+    <t>26:59 - 27:15</t>
+  </si>
+  <si>
+    <t>31:50 - 32:08</t>
+  </si>
+  <si>
+    <t>35:52 - 36:28</t>
+  </si>
+  <si>
+    <t>36:31 - 36:41</t>
+  </si>
+  <si>
+    <t>36:55 - 37:04</t>
+  </si>
+  <si>
+    <t>37:45 - 38:18</t>
+  </si>
+  <si>
+    <t>38:45 - 38:47</t>
+  </si>
+  <si>
+    <t>42:00 - 43:27</t>
+  </si>
+  <si>
+    <t>43:52 - 44:02</t>
+  </si>
+  <si>
+    <t>47:10 - 47:30</t>
+  </si>
+  <si>
+    <t>48:23 - 48:32</t>
+  </si>
+  <si>
+    <t>51:05 - 51:40</t>
+  </si>
+  <si>
+    <t>51:43 - 52:05</t>
+  </si>
+  <si>
+    <t>52:13 - 52:15</t>
+  </si>
+  <si>
+    <t>52:27 - 53:56</t>
+  </si>
+  <si>
+    <t>54:05 - 54:44</t>
+  </si>
+  <si>
+    <t>57:16 - 57:57</t>
+  </si>
+  <si>
+    <t>17:43 - 17:54</t>
+  </si>
+  <si>
+    <t>19:36 - 19:40</t>
+  </si>
+  <si>
+    <t>22:05 - 22:08</t>
+  </si>
+  <si>
+    <t>23:17 - 23:20</t>
+  </si>
+  <si>
+    <t>24:50 - 24:53</t>
+  </si>
+  <si>
+    <t>25:49 - 26:19</t>
+  </si>
+  <si>
+    <t>26:26 - 26:32</t>
+  </si>
+  <si>
+    <t>26:47 - 26:49</t>
+  </si>
+  <si>
+    <t>29::40 - 30:06</t>
+  </si>
+  <si>
+    <t>31:12 - 31:14</t>
+  </si>
+  <si>
+    <t>31:17 - 31:40</t>
+  </si>
+  <si>
+    <t>32:50 - 32:53</t>
+  </si>
+  <si>
+    <t>33:31 - 33:35</t>
+  </si>
+  <si>
+    <t>34:32 - 34:35</t>
+  </si>
+  <si>
+    <t>35:21 - 35:25</t>
+  </si>
+  <si>
+    <t>35:51 - 35:53</t>
+  </si>
+  <si>
+    <t>36:12 - 36:16</t>
+  </si>
+  <si>
+    <t>37:12 - 37:39</t>
+  </si>
+  <si>
+    <t>37:47 - 38:00</t>
+  </si>
+  <si>
+    <t>38:05 - 38:07</t>
+  </si>
+  <si>
+    <t>38:23 - 38:26</t>
+  </si>
+  <si>
+    <t>39:08 - 39:10</t>
+  </si>
+  <si>
+    <t>39:13 - 39:14</t>
+  </si>
+  <si>
+    <t>39:46 - 39:48</t>
+  </si>
+  <si>
+    <t>40:20 - 40:26</t>
+  </si>
+  <si>
+    <t>40:37 - 40:40</t>
+  </si>
+  <si>
+    <t>42:28 - 42:30</t>
+  </si>
+  <si>
+    <t>43:10 - 43:19</t>
+  </si>
+  <si>
+    <t>43:33 - 45:06</t>
+  </si>
+  <si>
+    <t>45:15 - 45:19</t>
+  </si>
+  <si>
+    <t>49:47 - 51:10</t>
+  </si>
+  <si>
+    <t>51:36 - 53:05</t>
+  </si>
+  <si>
+    <t>53:25 - 55:35</t>
+  </si>
+  <si>
+    <t>57:35 - 58:08</t>
+  </si>
+  <si>
+    <t>58:27 - 58:30</t>
+  </si>
+  <si>
+    <t>58:33 - 58:35</t>
+  </si>
+  <si>
+    <t>3:00 - 3:08</t>
+  </si>
+  <si>
+    <t>6:39 - 6:43</t>
+  </si>
+  <si>
+    <t>7:21 - 7:31</t>
+  </si>
+  <si>
+    <t>8:22 - 8:26</t>
+  </si>
+  <si>
+    <t>9:21 - 9:55</t>
+  </si>
+  <si>
+    <t>12:06 - 12:47</t>
+  </si>
+  <si>
+    <t>12:55 - 21:00</t>
+  </si>
+  <si>
+    <t>21:10 - 34:01</t>
+  </si>
+  <si>
+    <t>34:08 - 35:00</t>
+  </si>
+  <si>
+    <t>35:05 - 1:02:26</t>
+  </si>
+  <si>
+    <t>17:36 - 17:38</t>
+  </si>
+  <si>
+    <t>17:43 - 17:45</t>
+  </si>
+  <si>
+    <t>23:26 - 23:28</t>
+  </si>
+  <si>
+    <t>35:38 - 36:03</t>
+  </si>
+  <si>
+    <t>37:23 - 37:25</t>
+  </si>
+  <si>
+    <t>37:53 - 37:54</t>
+  </si>
+  <si>
+    <t>38:26 - 38:30</t>
+  </si>
+  <si>
+    <t>38:54 - 38:59</t>
+  </si>
+  <si>
+    <t>41:13 - 41:21</t>
+  </si>
+  <si>
+    <t>42:05 - 42:16</t>
+  </si>
+  <si>
+    <t>49:01 - 49:07</t>
+  </si>
+  <si>
+    <t>51:05 - 51:08</t>
+  </si>
+  <si>
+    <t>56:57 - 56:58</t>
+  </si>
+  <si>
+    <t>58:22 - 58:24</t>
+  </si>
+  <si>
+    <t>59:09 - 59:11</t>
+  </si>
+  <si>
+    <t>59:40 - 59:43</t>
+  </si>
+  <si>
+    <t>11:33 - 11:36</t>
+  </si>
+  <si>
+    <t>11:50 - 11:53</t>
+  </si>
+  <si>
+    <t>12:22 - 12:25</t>
+  </si>
+  <si>
+    <t>12:35 - 12:37</t>
+  </si>
+  <si>
+    <t>13:12 - 13:14</t>
+  </si>
+  <si>
+    <t>15:45 - 15:50</t>
+  </si>
+  <si>
+    <t>16:32 - 16:35</t>
+  </si>
+  <si>
+    <t>18:32 - 18:33</t>
+  </si>
+  <si>
+    <t>19:12 - 19:14</t>
+  </si>
+  <si>
+    <t>21:06 - 21:08</t>
+  </si>
+  <si>
+    <t>22:00 - 22:12</t>
+  </si>
+  <si>
+    <t>27:21 - 27:27</t>
+  </si>
+  <si>
+    <t>28:12 - 28:15</t>
+  </si>
+  <si>
+    <t>29:17 - 29:31</t>
+  </si>
+  <si>
+    <t>29:33 - 29:47</t>
+  </si>
+  <si>
+    <t>29:49 - 29:52</t>
+  </si>
+  <si>
+    <t>29:55 - 29:59</t>
+  </si>
+  <si>
+    <t>30:05 - 30:14</t>
+  </si>
+  <si>
+    <t>30:23 - 30:26</t>
+  </si>
+  <si>
+    <t>31:17 - 31:21</t>
+  </si>
+  <si>
+    <t>32:00 - 32:18</t>
+  </si>
+  <si>
+    <t>32:25 - 32:31</t>
+  </si>
+  <si>
+    <t>32:45 - 32:49</t>
+  </si>
+  <si>
+    <t>33:40 - 33:47</t>
+  </si>
+  <si>
+    <t>44:53 - 45:15</t>
+  </si>
+  <si>
+    <t>47:09 - 47:11</t>
+  </si>
+  <si>
+    <t>50:40 - 50:44</t>
+  </si>
+  <si>
+    <t>51:22 - 51:24</t>
+  </si>
+  <si>
+    <t>52:58 - 53:05</t>
+  </si>
+  <si>
+    <t>55:11 - 55:15</t>
+  </si>
+  <si>
+    <t>55:18 - 55:20</t>
+  </si>
+  <si>
+    <t>28:10 - 28:28</t>
+  </si>
+  <si>
+    <t>33:39 - 33:50</t>
+  </si>
+  <si>
+    <t>34:01 - 34:28</t>
+  </si>
+  <si>
+    <t>34:45 - 34:46</t>
+  </si>
+  <si>
+    <t>38:43 - 39:33</t>
+  </si>
+  <si>
+    <t>39:41 - 39:44</t>
+  </si>
+  <si>
+    <t>40:25 - 40:26</t>
+  </si>
+  <si>
+    <t>41:11 - 41:13</t>
+  </si>
+  <si>
+    <t>41:26 - 41:27</t>
+  </si>
+  <si>
+    <t>41:59 - 42:01</t>
+  </si>
+  <si>
+    <t>42:06 - 42:07</t>
+  </si>
+  <si>
+    <t>42:31 - 42:34</t>
+  </si>
+  <si>
+    <t>43:32 - 43:36</t>
+  </si>
+  <si>
+    <t>44:44 - 44:46</t>
+  </si>
+  <si>
+    <t>45:38 - 45:42</t>
+  </si>
+  <si>
+    <t>45:51 - 45:53</t>
+  </si>
+  <si>
+    <t>47:48 - 48:00</t>
+  </si>
+  <si>
+    <t>48:31 - 48:35</t>
+  </si>
+  <si>
+    <t>50:21 - 50:22</t>
+  </si>
+  <si>
+    <t>50:55 - 50:57</t>
+  </si>
+  <si>
+    <t>51:05 - 51:06</t>
+  </si>
+  <si>
+    <t>52:22 - 52:27</t>
+  </si>
+  <si>
+    <t>52:37 - 52:40</t>
+  </si>
+  <si>
+    <t>52:46 - 52:47</t>
+  </si>
+  <si>
+    <t>53:04 - 53:05</t>
+  </si>
+  <si>
+    <t>54:22 - 55:06</t>
+  </si>
+  <si>
+    <t>55:10 - 55:14</t>
+  </si>
+  <si>
+    <t>55:23 - 55:31</t>
+  </si>
+  <si>
+    <t>56:12 - 56:15</t>
+  </si>
+  <si>
+    <t>56:21 - 56:30</t>
+  </si>
+  <si>
+    <t>58:33 - 58:38</t>
+  </si>
+  <si>
+    <t>59:03 - 59:11</t>
+  </si>
+  <si>
+    <t>18:18 - 18:20</t>
+  </si>
+  <si>
+    <t>30:04 - 30:06</t>
+  </si>
+  <si>
+    <t>30:23 - 30:25</t>
+  </si>
+  <si>
+    <t>32:58 - 33:04</t>
+  </si>
+  <si>
+    <t>33:16 - 33:19</t>
+  </si>
+  <si>
+    <t>34:15 - 34:20</t>
+  </si>
+  <si>
+    <t>44:13 - 44:15</t>
+  </si>
+  <si>
+    <t>44:19 - 44:22</t>
+  </si>
+  <si>
+    <t>47:28 - 47:34</t>
+  </si>
+  <si>
+    <t>48:03 - 48:07</t>
+  </si>
+  <si>
+    <t>49:43 - 49:46</t>
+  </si>
+  <si>
+    <t>50:17 - 50:18</t>
+  </si>
+  <si>
+    <t>50:27 - 50:29</t>
+  </si>
+  <si>
+    <t>50:40 - 50:46</t>
+  </si>
+  <si>
+    <t>51:08 - 51:09</t>
+  </si>
+  <si>
+    <t>51:21 - 51:25</t>
+  </si>
+  <si>
+    <t>51:57 - 51:59</t>
+  </si>
+  <si>
+    <t>53:56 - 54:26</t>
+  </si>
+  <si>
+    <t>55:30 - 55:34</t>
+  </si>
+  <si>
+    <t>56:38 - 56:42</t>
+  </si>
+  <si>
+    <t>57:56 - 57:58</t>
+  </si>
+  <si>
+    <t>58:31 - 58:34</t>
+  </si>
+  <si>
+    <t>58:51 - 59:07</t>
+  </si>
+  <si>
+    <t>59:11 - 59:13</t>
+  </si>
+  <si>
+    <t>59:16 - 59:39</t>
+  </si>
+  <si>
+    <t>59:47 - 59:49</t>
+  </si>
+  <si>
+    <t>1:00:00 - 1:00:01</t>
+  </si>
+  <si>
+    <t>5:22 - 5:28</t>
+  </si>
+  <si>
+    <t>24:11 - 24:24</t>
+  </si>
+  <si>
+    <t>28:46 - 29:39</t>
+  </si>
+  <si>
+    <t>31:55 - 31:56</t>
+  </si>
+  <si>
+    <t>34:04 - 34:18</t>
+  </si>
+  <si>
+    <t>36:02 - 36:04</t>
+  </si>
+  <si>
+    <t>37:52 - 37:55</t>
+  </si>
+  <si>
+    <t>38:14 - 38:17</t>
+  </si>
+  <si>
+    <t>39:07 - 39:10</t>
+  </si>
+  <si>
+    <t>39:21 - 39:24</t>
+  </si>
+  <si>
+    <t>40:04 - 40:06</t>
+  </si>
+  <si>
+    <t>40:17 - 40:18</t>
+  </si>
+  <si>
+    <t>40:37 - 40:39</t>
+  </si>
+  <si>
+    <t>41:01 - 41:03</t>
+  </si>
+  <si>
+    <t>42:01 - 42:07</t>
+  </si>
+  <si>
+    <t>42:32 - 42:34</t>
+  </si>
+  <si>
+    <t>43:07 - 43:09</t>
+  </si>
+  <si>
+    <t>44:18 - 44:22</t>
+  </si>
+  <si>
+    <t>44:32 - 44:34</t>
+  </si>
+  <si>
+    <t>44:54 - 44:56</t>
+  </si>
+  <si>
+    <t>45:10 - 45:12</t>
+  </si>
+  <si>
+    <t>45:23 - 45:26</t>
+  </si>
+  <si>
+    <t>46:12 - 46:22</t>
+  </si>
+  <si>
+    <t>46:44 - 46:48</t>
+  </si>
+  <si>
+    <t>48:21 - 48:29</t>
+  </si>
+  <si>
+    <t>49:54 - 50:00</t>
   </si>
 </sst>
 </file>
@@ -630,7 +1633,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -649,6 +1652,15 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -661,7 +1673,71 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing25.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -953,6 +2029,2197 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C17" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C24" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C25" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="7">
+        <v>45693.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" s="7">
+        <v>45693.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45660.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" s="7">
+        <v>45660.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C11" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="7">
+        <v>45659.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C25" s="7">
+        <v>45660.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C28" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C30" s="7">
+        <v>45660.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C32" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C33" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C34" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C35" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C37" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C38" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C39" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C42" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C44" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C45" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C48" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C50" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C51" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C52" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C53" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C54" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C55" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C56" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C58" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C59" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C60" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C61" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C62" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C63" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C64" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C4" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C7" s="7">
+        <v>45693.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C9" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C13" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C14" s="7">
+        <v>45659.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C15" s="7">
+        <v>45659.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C20" s="7">
+        <v>45693.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C21" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C23" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C25" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C28" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C29" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C30" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C31" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C32" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C33" s="7">
+        <v>45693.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C34" s="7">
+        <v>45693.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C7" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C10" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C19" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C20" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C30" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C31" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C32" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C33" s="7">
+        <v>45660.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C34" s="7">
+        <v>45659.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C9" s="7">
+        <v>45662.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C10" s="7">
+        <v>45691.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C11" s="7">
+        <v>45660.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C22" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C23" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C24" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C25" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C26" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C27" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C28" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C29" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C30" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C31" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C32" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
@@ -4048,6 +7315,830 @@
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C6" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C7" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46024.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C19" s="7">
+        <v>46024.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29">
+      <c r="C29" s="1"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/data/seizure_stage.xlsx
+++ b/data/seizure_stage.xlsx
@@ -3,31 +3,54 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Seizure Stage" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="112625F1" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="112625F1_B" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="112725F2" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="112725F2_B" sheetId="5" r:id="rId8"/>
-    <sheet state="visible" name="112625M1" sheetId="6" r:id="rId9"/>
-    <sheet state="visible" name="112625M1_B" sheetId="7" r:id="rId10"/>
-    <sheet state="visible" name="112625M2" sheetId="8" r:id="rId11"/>
-    <sheet state="visible" name="112625M2_B" sheetId="9" r:id="rId12"/>
-    <sheet state="visible" name="120725M1" sheetId="10" r:id="rId13"/>
-    <sheet state="visible" name="120725M1_B" sheetId="11" r:id="rId14"/>
-    <sheet state="visible" name="120725F1" sheetId="12" r:id="rId15"/>
-    <sheet state="visible" name="120725F1_B" sheetId="13" r:id="rId16"/>
-    <sheet state="visible" name="120725F2" sheetId="14" r:id="rId17"/>
-    <sheet state="visible" name="120725F2_B" sheetId="15" r:id="rId18"/>
-    <sheet state="visible" name="121125F1" sheetId="16" r:id="rId19"/>
-    <sheet state="visible" name="121125F1_B" sheetId="17" r:id="rId20"/>
-    <sheet state="visible" name="121125M1" sheetId="18" r:id="rId21"/>
-    <sheet state="visible" name="121125M1_B" sheetId="19" r:id="rId22"/>
-    <sheet state="visible" name="121125M2" sheetId="20" r:id="rId23"/>
-    <sheet state="visible" name="121125M2_B" sheetId="21" r:id="rId24"/>
-    <sheet state="visible" name="121225F1" sheetId="22" r:id="rId25"/>
-    <sheet state="visible" name="121225F1_B" sheetId="23" r:id="rId26"/>
-    <sheet state="visible" name="121225F2" sheetId="24" r:id="rId27"/>
-    <sheet state="visible" name="121225F2_B" sheetId="25" r:id="rId28"/>
+    <sheet state="visible" name="Seizure Stage" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="112625F1" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="112625F1_B" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="112725F2" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="112725F2_B" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="112625M1" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="112625M1_B" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="112625M2" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="112625M2_B" sheetId="9" r:id="rId13"/>
+    <sheet state="visible" name="120725M1" sheetId="10" r:id="rId14"/>
+    <sheet state="visible" name="120725M1_B" sheetId="11" r:id="rId15"/>
+    <sheet state="visible" name="120725F1" sheetId="12" r:id="rId16"/>
+    <sheet state="visible" name="120725F1_B" sheetId="13" r:id="rId17"/>
+    <sheet state="visible" name="120725F2" sheetId="14" r:id="rId18"/>
+    <sheet state="visible" name="120725F2_B" sheetId="15" r:id="rId19"/>
+    <sheet state="visible" name="121125F1" sheetId="16" r:id="rId20"/>
+    <sheet state="visible" name="121125F1_B" sheetId="17" r:id="rId21"/>
+    <sheet state="visible" name="121125M1" sheetId="18" r:id="rId22"/>
+    <sheet state="visible" name="121125M1_B" sheetId="19" r:id="rId23"/>
+    <sheet state="visible" name="121125M2" sheetId="20" r:id="rId24"/>
+    <sheet state="visible" name="121125M2_B" sheetId="21" r:id="rId25"/>
+    <sheet state="visible" name="121225F1" sheetId="22" r:id="rId26"/>
+    <sheet state="visible" name="121225F1_B" sheetId="23" r:id="rId27"/>
+    <sheet state="visible" name="121225F2" sheetId="24" r:id="rId28"/>
+    <sheet state="visible" name="121225F2_B" sheetId="25" r:id="rId29"/>
+    <sheet state="visible" name="121225M1" sheetId="26" r:id="rId30"/>
+    <sheet state="visible" name="121225M1_B" sheetId="27" r:id="rId31"/>
+    <sheet state="visible" name="121325M1" sheetId="28" r:id="rId32"/>
+    <sheet state="visible" name="121325M1_B" sheetId="29" r:id="rId33"/>
+    <sheet state="visible" name="121325M2" sheetId="30" r:id="rId34"/>
+    <sheet state="visible" name="121325M2_B" sheetId="31" r:id="rId35"/>
+    <sheet state="visible" name="121325M3" sheetId="32" r:id="rId36"/>
+    <sheet state="visible" name="121325M3_B1" sheetId="33" r:id="rId37"/>
+    <sheet state="visible" name="121325M3_B2" sheetId="34" r:id="rId38"/>
+    <sheet state="visible" name="121425F1" sheetId="35" r:id="rId39"/>
+    <sheet state="visible" name="121425F1_B" sheetId="36" r:id="rId40"/>
+    <sheet state="visible" name="121425F2" sheetId="37" r:id="rId41"/>
+    <sheet state="visible" name="121425F2_B" sheetId="38" r:id="rId42"/>
+    <sheet state="visible" name="121525F1" sheetId="39" r:id="rId43"/>
+    <sheet state="visible" name="121525F1_B" sheetId="40" r:id="rId44"/>
+    <sheet state="visible" name="121525F2" sheetId="41" r:id="rId45"/>
+    <sheet state="visible" name="121525F2_B" sheetId="42" r:id="rId46"/>
+    <sheet state="visible" name="121525F3" sheetId="43" r:id="rId47"/>
+    <sheet state="visible" name="121525F3_B" sheetId="44" r:id="rId48"/>
+    <sheet state="visible" name="010626F1" sheetId="45" r:id="rId49"/>
+    <sheet state="visible" name="010626F1_B" sheetId="46" r:id="rId50"/>
+    <sheet state="visible" name="010626F2" sheetId="47" r:id="rId51"/>
+    <sheet state="visible" name="010626F2_B" sheetId="48" r:id="rId52"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -35,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="1185">
   <si>
     <t>Stage</t>
   </si>
@@ -673,7 +696,7 @@
     <t>44:50 - 44:52</t>
   </si>
   <si>
-    <t>46:33 - 36:42</t>
+    <t>46:33 - 46:42</t>
   </si>
   <si>
     <t>47:20 - 47:26</t>
@@ -1075,7 +1098,7 @@
     <t>26:47 - 26:49</t>
   </si>
   <si>
-    <t>29::40 - 30:06</t>
+    <t>29:40 - 30:06</t>
   </si>
   <si>
     <t>31:12 - 31:14</t>
@@ -1237,6 +1260,156 @@
     <t>59:40 - 59:43</t>
   </si>
   <si>
+    <t>9:16 - 9:49</t>
+  </si>
+  <si>
+    <t>14:49 - 14:53</t>
+  </si>
+  <si>
+    <t>15:57 - 16:29</t>
+  </si>
+  <si>
+    <t>17:01 - 17:03</t>
+  </si>
+  <si>
+    <t>17:30 - 19:00</t>
+  </si>
+  <si>
+    <t>19:33 - 19:38</t>
+  </si>
+  <si>
+    <t>23:02 - 23:42</t>
+  </si>
+  <si>
+    <t>23:49 - 24:08</t>
+  </si>
+  <si>
+    <t>24:18 - 24:23</t>
+  </si>
+  <si>
+    <t>24:29 - 24:32</t>
+  </si>
+  <si>
+    <t>24:36 - 24:39</t>
+  </si>
+  <si>
+    <t>25:28 - 25:36</t>
+  </si>
+  <si>
+    <t>25:42 - 25:45</t>
+  </si>
+  <si>
+    <t>26:16 - 26:22</t>
+  </si>
+  <si>
+    <t>26:54 - 28:02</t>
+  </si>
+  <si>
+    <t>28:11 - 28:19</t>
+  </si>
+  <si>
+    <t>29:42 - 30:03</t>
+  </si>
+  <si>
+    <t>30:08 - 30:13</t>
+  </si>
+  <si>
+    <t>30:35 - 30:41</t>
+  </si>
+  <si>
+    <t>31:38 - 32:18</t>
+  </si>
+  <si>
+    <t>32:23 - 32:58</t>
+  </si>
+  <si>
+    <t>33:05 - 33:37</t>
+  </si>
+  <si>
+    <t>33:49 - 33:56</t>
+  </si>
+  <si>
+    <t>35:03 - 35:37</t>
+  </si>
+  <si>
+    <t>35:44 - 36:02</t>
+  </si>
+  <si>
+    <t>36:07 - 37:50</t>
+  </si>
+  <si>
+    <t>37:58 - 38:46</t>
+  </si>
+  <si>
+    <t>40:15 - 40:27</t>
+  </si>
+  <si>
+    <t>41:45 - 41:49</t>
+  </si>
+  <si>
+    <t>42:16 - 42:30</t>
+  </si>
+  <si>
+    <t>45:22 - 45:30</t>
+  </si>
+  <si>
+    <t>46:53 - 46:59</t>
+  </si>
+  <si>
+    <t>47:28 - 47:39</t>
+  </si>
+  <si>
+    <t>47:52 - 48:13</t>
+  </si>
+  <si>
+    <t>48:18 - 48:36</t>
+  </si>
+  <si>
+    <t>48:43 - 48:47</t>
+  </si>
+  <si>
+    <t>49:14 - 49:25</t>
+  </si>
+  <si>
+    <t>50:41 - 50:48</t>
+  </si>
+  <si>
+    <t>50:54 - 50:58</t>
+  </si>
+  <si>
+    <t>51:10 - 51:32</t>
+  </si>
+  <si>
+    <t>51:38 - 52:22</t>
+  </si>
+  <si>
+    <t>52:33 - 52:59</t>
+  </si>
+  <si>
+    <t>53:31 - 53:42</t>
+  </si>
+  <si>
+    <t>53:58 - 54:48</t>
+  </si>
+  <si>
+    <t>55:01 - 55:23</t>
+  </si>
+  <si>
+    <t>57:10 - 58:10</t>
+  </si>
+  <si>
+    <t>59:15 - 59:33</t>
+  </si>
+  <si>
+    <t>1:00:34 - 1:00:56</t>
+  </si>
+  <si>
+    <t>1:01:15 - 1:01:18</t>
+  </si>
+  <si>
+    <t>1:01:23 - 1:01:57</t>
+  </si>
+  <si>
     <t>11:33 - 11:36</t>
   </si>
   <si>
@@ -1330,6 +1503,111 @@
     <t>55:18 - 55:20</t>
   </si>
   <si>
+    <t>2:51 - 3:20</t>
+  </si>
+  <si>
+    <t>6:24 - 6:27</t>
+  </si>
+  <si>
+    <t>6:57 - 7:21</t>
+  </si>
+  <si>
+    <t>10:33 - 10:38</t>
+  </si>
+  <si>
+    <t>10:48 - 10:51</t>
+  </si>
+  <si>
+    <t>31:38 - 32:36</t>
+  </si>
+  <si>
+    <t>33:07 - 33:34</t>
+  </si>
+  <si>
+    <t>33:42 - 33:55</t>
+  </si>
+  <si>
+    <t>34:05 - 34:33</t>
+  </si>
+  <si>
+    <t>34:44 - 34:47</t>
+  </si>
+  <si>
+    <t>35:16 - 35:28</t>
+  </si>
+  <si>
+    <t>35:42 - 35:45</t>
+  </si>
+  <si>
+    <t>36:33 - 36:37</t>
+  </si>
+  <si>
+    <t>37:08 - 37:14</t>
+  </si>
+  <si>
+    <t>37:32 - 38:31</t>
+  </si>
+  <si>
+    <t>38:34 - 38:45</t>
+  </si>
+  <si>
+    <t>38:50 - 39:33</t>
+  </si>
+  <si>
+    <t>39:38 - 39:50</t>
+  </si>
+  <si>
+    <t>40:01 - 42:14</t>
+  </si>
+  <si>
+    <t>42:31 - 42:35</t>
+  </si>
+  <si>
+    <t>43:00 - 44:05</t>
+  </si>
+  <si>
+    <t>44:27 - 44:32</t>
+  </si>
+  <si>
+    <t>44:36 - 45:05</t>
+  </si>
+  <si>
+    <t>45:14 - 47:47</t>
+  </si>
+  <si>
+    <t>47:52 - 48:04</t>
+  </si>
+  <si>
+    <t>48:08 - 48:44</t>
+  </si>
+  <si>
+    <t>49:19 - 49:30</t>
+  </si>
+  <si>
+    <t>52:59 - 53:05</t>
+  </si>
+  <si>
+    <t>53:18 - 55:22</t>
+  </si>
+  <si>
+    <t>55:42 - 55:46</t>
+  </si>
+  <si>
+    <t>56:58 - 58:49</t>
+  </si>
+  <si>
+    <t>58:56 - 59:19</t>
+  </si>
+  <si>
+    <t>59:27 - 59:37</t>
+  </si>
+  <si>
+    <t>59:45 - 59:48</t>
+  </si>
+  <si>
+    <t>59:54 - 1:00:14</t>
+  </si>
+  <si>
     <t>28:10 - 28:28</t>
   </si>
   <si>
@@ -1426,6 +1704,108 @@
     <t>59:03 - 59:11</t>
   </si>
   <si>
+    <t>2:19 - 3:09</t>
+  </si>
+  <si>
+    <t>3:18 - 3:23</t>
+  </si>
+  <si>
+    <t>4:15 - 4:31</t>
+  </si>
+  <si>
+    <t>5:27 - 5:29</t>
+  </si>
+  <si>
+    <t>7:44 - 8:12</t>
+  </si>
+  <si>
+    <t>8:59 - 9:02</t>
+  </si>
+  <si>
+    <t>9:24 - 14:06</t>
+  </si>
+  <si>
+    <t>14:10 - 14:38</t>
+  </si>
+  <si>
+    <t>15:37 - 15:50</t>
+  </si>
+  <si>
+    <t>15:55 - 16:06</t>
+  </si>
+  <si>
+    <t>16:33 - 16:57</t>
+  </si>
+  <si>
+    <t>17:07 - 17:46</t>
+  </si>
+  <si>
+    <t>18:02 - 18:08</t>
+  </si>
+  <si>
+    <t>18:16 - 19:00</t>
+  </si>
+  <si>
+    <t>19:14 - 20:40</t>
+  </si>
+  <si>
+    <t>20:45 - 20:53</t>
+  </si>
+  <si>
+    <t>21:06 - 21:17</t>
+  </si>
+  <si>
+    <t>21:32 - 21:39</t>
+  </si>
+  <si>
+    <t>23:03 - 23:16</t>
+  </si>
+  <si>
+    <t>24:55 - 25:13</t>
+  </si>
+  <si>
+    <t>25:25 - 25:43</t>
+  </si>
+  <si>
+    <t>26:03 - 26:16</t>
+  </si>
+  <si>
+    <t>26:33 - 27:23</t>
+  </si>
+  <si>
+    <t>27:47 - 28:11</t>
+  </si>
+  <si>
+    <t>29:13 - 29:31</t>
+  </si>
+  <si>
+    <t>30:08 - 32:37</t>
+  </si>
+  <si>
+    <t>32:44 - 34:05</t>
+  </si>
+  <si>
+    <t>35:53 - 38:10</t>
+  </si>
+  <si>
+    <t>38:24 - 42:32</t>
+  </si>
+  <si>
+    <t>42:36 - 42:53</t>
+  </si>
+  <si>
+    <t>43:16 - 46:18</t>
+  </si>
+  <si>
+    <t>46:45 - 56:04</t>
+  </si>
+  <si>
+    <t>56:12 - 57:56</t>
+  </si>
+  <si>
+    <t>58:02 - 1:03:38</t>
+  </si>
+  <si>
     <t>18:18 - 18:20</t>
   </si>
   <si>
@@ -1507,6 +1887,189 @@
     <t>1:00:00 - 1:00:01</t>
   </si>
   <si>
+    <t>0:05 - 0:13</t>
+  </si>
+  <si>
+    <t>5:40 - 5:48</t>
+  </si>
+  <si>
+    <t>14:07 - 14:18</t>
+  </si>
+  <si>
+    <t>17:15 - 17:18</t>
+  </si>
+  <si>
+    <t>18:43 -  19:07</t>
+  </si>
+  <si>
+    <t>19:33 - 19:37</t>
+  </si>
+  <si>
+    <t>19:42 - 19:48</t>
+  </si>
+  <si>
+    <t>21:41 - 21:46</t>
+  </si>
+  <si>
+    <t>22:54 - 23:06</t>
+  </si>
+  <si>
+    <t>24:09 - 24:18</t>
+  </si>
+  <si>
+    <t>25:13 - 25:20</t>
+  </si>
+  <si>
+    <t>28:35 - 29:05</t>
+  </si>
+  <si>
+    <t>29:21 - 29:23</t>
+  </si>
+  <si>
+    <t>30:29 - 30:44</t>
+  </si>
+  <si>
+    <t>30:51 - 30:57</t>
+  </si>
+  <si>
+    <t>31:51 - 32:01</t>
+  </si>
+  <si>
+    <t>35:39 - 35:57</t>
+  </si>
+  <si>
+    <t>36:24 - 36:27</t>
+  </si>
+  <si>
+    <t>36:34 - 36:40</t>
+  </si>
+  <si>
+    <t>36:54 - 36:56</t>
+  </si>
+  <si>
+    <t>37:00 - 37:04</t>
+  </si>
+  <si>
+    <t>37:31 - 37:38</t>
+  </si>
+  <si>
+    <t>38:34 - 38:39</t>
+  </si>
+  <si>
+    <t>38:58 - 39:00</t>
+  </si>
+  <si>
+    <t>39:29 - 40:10</t>
+  </si>
+  <si>
+    <t>40:45 - 41:03</t>
+  </si>
+  <si>
+    <t>41:08 - 41:34</t>
+  </si>
+  <si>
+    <t>41:45 - 42:13</t>
+  </si>
+  <si>
+    <t>42:44 - 42:48</t>
+  </si>
+  <si>
+    <t>43:05 - 43:09</t>
+  </si>
+  <si>
+    <t>43:13 - 43:25</t>
+  </si>
+  <si>
+    <t>43:31 - 43:33</t>
+  </si>
+  <si>
+    <t>43:58 - 44:05</t>
+  </si>
+  <si>
+    <t>45:25 - 45:31</t>
+  </si>
+  <si>
+    <t>45:33 - 45:44</t>
+  </si>
+  <si>
+    <t>45:53 - 47:14</t>
+  </si>
+  <si>
+    <t>47:17 - 47:19</t>
+  </si>
+  <si>
+    <t>47:24 - 47:44</t>
+  </si>
+  <si>
+    <t>47:53 - 48:05</t>
+  </si>
+  <si>
+    <t>48:15 - 48:17</t>
+  </si>
+  <si>
+    <t>48:43 - 48:52</t>
+  </si>
+  <si>
+    <t>48:58 - 49:20</t>
+  </si>
+  <si>
+    <t>49:36 - 49:42</t>
+  </si>
+  <si>
+    <t>49:57 - 50:03</t>
+  </si>
+  <si>
+    <t>50:12 - 50:16</t>
+  </si>
+  <si>
+    <t>50:31 - 50:57</t>
+  </si>
+  <si>
+    <t>51:27 - 52:37</t>
+  </si>
+  <si>
+    <t>52:42 - 53:08</t>
+  </si>
+  <si>
+    <t>53:13 - 53:23</t>
+  </si>
+  <si>
+    <t>53:27 - 54:16</t>
+  </si>
+  <si>
+    <t>54:23 - 54:46</t>
+  </si>
+  <si>
+    <t>54:51 - 55:44</t>
+  </si>
+  <si>
+    <t>56:48 - 56:54</t>
+  </si>
+  <si>
+    <t>57:02 - 57:04</t>
+  </si>
+  <si>
+    <t>57:07 - 57:27</t>
+  </si>
+  <si>
+    <t>57:31 - 57:36</t>
+  </si>
+  <si>
+    <t>58:02 - 58:48</t>
+  </si>
+  <si>
+    <t>58:57 - 59:00</t>
+  </si>
+  <si>
+    <t>59:08 - 59:10</t>
+  </si>
+  <si>
+    <t>59:13 - 59:26</t>
+  </si>
+  <si>
+    <t>59:34 - 59:42</t>
+  </si>
+  <si>
     <t>5:22 - 5:28</t>
   </si>
   <si>
@@ -1583,6 +2146,1473 @@
   </si>
   <si>
     <t>49:54 - 50:00</t>
+  </si>
+  <si>
+    <t>51:40 - 51:42</t>
+  </si>
+  <si>
+    <t>54:58 - 55:21</t>
+  </si>
+  <si>
+    <t>55:33 - 55:35</t>
+  </si>
+  <si>
+    <t>57:28 - 57:36</t>
+  </si>
+  <si>
+    <t>57:40 - 57:49</t>
+  </si>
+  <si>
+    <t>57:59 - 58:00</t>
+  </si>
+  <si>
+    <t>1:00 - 1:04</t>
+  </si>
+  <si>
+    <t>1:07 - 1:42</t>
+  </si>
+  <si>
+    <t>3:26 - 3:34</t>
+  </si>
+  <si>
+    <t>5:35 - 5:58</t>
+  </si>
+  <si>
+    <t>6:34 - 6:48</t>
+  </si>
+  <si>
+    <t>6:51 - 6:56</t>
+  </si>
+  <si>
+    <t>7:02 - 7:13</t>
+  </si>
+  <si>
+    <t>7:35 - 8:30</t>
+  </si>
+  <si>
+    <t>10:24 - 10:28</t>
+  </si>
+  <si>
+    <t>11:12 - 11:14</t>
+  </si>
+  <si>
+    <t>11:39 - 11:41</t>
+  </si>
+  <si>
+    <t>12:56 - 12:59</t>
+  </si>
+  <si>
+    <t>13:43 - 13:45</t>
+  </si>
+  <si>
+    <t>13:52 - 13:59</t>
+  </si>
+  <si>
+    <t>14:09 - 14:12</t>
+  </si>
+  <si>
+    <t>14:14 - 14:26</t>
+  </si>
+  <si>
+    <t>14:32 - 15:40</t>
+  </si>
+  <si>
+    <t>15:58 - 16:13</t>
+  </si>
+  <si>
+    <t>17:17 - 18:15</t>
+  </si>
+  <si>
+    <t>18:19 - 18:38</t>
+  </si>
+  <si>
+    <t>18:51 - 19:28</t>
+  </si>
+  <si>
+    <t>19:42 - 20:04</t>
+  </si>
+  <si>
+    <t>21:34 - 21:38</t>
+  </si>
+  <si>
+    <t>21:58 - 22:01</t>
+  </si>
+  <si>
+    <t>22:04 - 22:08</t>
+  </si>
+  <si>
+    <t>22:20 - 22:31</t>
+  </si>
+  <si>
+    <t>22:37 - 22:43</t>
+  </si>
+  <si>
+    <t>23:00 - 23:05</t>
+  </si>
+  <si>
+    <t>23:20 - 23:27</t>
+  </si>
+  <si>
+    <t>23:44 - 23:48</t>
+  </si>
+  <si>
+    <t>24:16 - 24:20</t>
+  </si>
+  <si>
+    <t>24:27 - 24:33</t>
+  </si>
+  <si>
+    <t>24:54 - 25:03</t>
+  </si>
+  <si>
+    <t>25:27 - 26:40</t>
+  </si>
+  <si>
+    <t>27:18 - 29:46</t>
+  </si>
+  <si>
+    <t>30:38 - 35:20</t>
+  </si>
+  <si>
+    <t>36:20 - 39:10</t>
+  </si>
+  <si>
+    <t>39:17 - 39:27</t>
+  </si>
+  <si>
+    <t>39:32 - 39:39</t>
+  </si>
+  <si>
+    <t>39:53 - 39:59</t>
+  </si>
+  <si>
+    <t>41:20 - 42:12</t>
+  </si>
+  <si>
+    <t>42:18 - 42:40</t>
+  </si>
+  <si>
+    <t>43:02 - 43:12</t>
+  </si>
+  <si>
+    <t>43:18 - 43:45</t>
+  </si>
+  <si>
+    <t>43:57 - 44:35</t>
+  </si>
+  <si>
+    <t>44:37 - 45:32</t>
+  </si>
+  <si>
+    <t>45:56 - 47:31</t>
+  </si>
+  <si>
+    <t>47:39 - 1:00:01</t>
+  </si>
+  <si>
+    <t>31:00 - 33:10</t>
+  </si>
+  <si>
+    <t>35:24 - 36:19</t>
+  </si>
+  <si>
+    <t>39:41 - 40:37</t>
+  </si>
+  <si>
+    <t>41:56 - 43:55</t>
+  </si>
+  <si>
+    <t>44:08 - 44:16</t>
+  </si>
+  <si>
+    <t>51:04 - 51:28</t>
+  </si>
+  <si>
+    <t>51:32 - 52:46</t>
+  </si>
+  <si>
+    <t>53:10 - 53:22</t>
+  </si>
+  <si>
+    <t>55:27 - 55:29</t>
+  </si>
+  <si>
+    <t>59:00 - 1:00:02</t>
+  </si>
+  <si>
+    <t>0:00 - 1:52</t>
+  </si>
+  <si>
+    <t>8:31 - 9:23</t>
+  </si>
+  <si>
+    <t>10:24 - 10:32</t>
+  </si>
+  <si>
+    <t>11:09 - 11:15</t>
+  </si>
+  <si>
+    <t>16:31 - 16:35</t>
+  </si>
+  <si>
+    <t>16:49 - 23:17</t>
+  </si>
+  <si>
+    <t>43:04 - 44:47</t>
+  </si>
+  <si>
+    <t>46:19 - 46:27</t>
+  </si>
+  <si>
+    <t>58:10 - 58:47</t>
+  </si>
+  <si>
+    <t>59:00 - 59:31</t>
+  </si>
+  <si>
+    <t>59:39 - 1:00:02</t>
+  </si>
+  <si>
+    <t>27:14 - 27:23</t>
+  </si>
+  <si>
+    <t>30:56 - 31:00</t>
+  </si>
+  <si>
+    <t>31:32 - 31:36</t>
+  </si>
+  <si>
+    <t>33:18 - 33:53</t>
+  </si>
+  <si>
+    <t>36:09 - 36:12</t>
+  </si>
+  <si>
+    <t>36:35 - 36:38</t>
+  </si>
+  <si>
+    <t>37:17 - 37:20</t>
+  </si>
+  <si>
+    <t>37:56 - 37:59</t>
+  </si>
+  <si>
+    <t>38:20 - 38:24</t>
+  </si>
+  <si>
+    <t>38:50 - 38:53</t>
+  </si>
+  <si>
+    <t>39:11 - 39:13</t>
+  </si>
+  <si>
+    <t>39:22 - 39:24</t>
+  </si>
+  <si>
+    <t>40:19 - 40:23</t>
+  </si>
+  <si>
+    <t>40:56 - 40:59</t>
+  </si>
+  <si>
+    <t>41:15 - 41:19</t>
+  </si>
+  <si>
+    <t>41:42 - 41:47</t>
+  </si>
+  <si>
+    <t>42:19 - 42:22</t>
+  </si>
+  <si>
+    <t>43:00 - 43:03</t>
+  </si>
+  <si>
+    <t>44:14 - 44:17</t>
+  </si>
+  <si>
+    <t>45:02 - 45:05</t>
+  </si>
+  <si>
+    <t>46:19 - 46:23</t>
+  </si>
+  <si>
+    <t>47:12 - 47:18</t>
+  </si>
+  <si>
+    <t>47:34 - 47:36</t>
+  </si>
+  <si>
+    <t>48:25 - 48:31</t>
+  </si>
+  <si>
+    <t>49:02 - 49:06</t>
+  </si>
+  <si>
+    <t>50:07 - 50:19</t>
+  </si>
+  <si>
+    <t>50:51 - 50:54</t>
+  </si>
+  <si>
+    <t>51:37 - 51:47</t>
+  </si>
+  <si>
+    <t>51:53 - 51:56</t>
+  </si>
+  <si>
+    <t>52:13 - 52:17</t>
+  </si>
+  <si>
+    <t>52:33 - 52:36</t>
+  </si>
+  <si>
+    <t>53:29 - 53:33</t>
+  </si>
+  <si>
+    <t>53:58 - 54:00</t>
+  </si>
+  <si>
+    <t>54:51 - 55:00</t>
+  </si>
+  <si>
+    <t>55:23 - 55:28</t>
+  </si>
+  <si>
+    <t>56:46 - 57:11</t>
+  </si>
+  <si>
+    <t>57:34 - 57:42</t>
+  </si>
+  <si>
+    <t>57:52 - 58:35</t>
+  </si>
+  <si>
+    <t>59:18 - 59:23</t>
+  </si>
+  <si>
+    <t>1:00:05 - 1:00:18</t>
+  </si>
+  <si>
+    <t>1:00:42 - 1:00:46</t>
+  </si>
+  <si>
+    <t>1:00:56 - 1:01:00</t>
+  </si>
+  <si>
+    <t>0:08 - 0:45</t>
+  </si>
+  <si>
+    <t>0:52 - 1:33</t>
+  </si>
+  <si>
+    <t>1:37 - 1:39</t>
+  </si>
+  <si>
+    <t>1:43 - 1:51</t>
+  </si>
+  <si>
+    <t>2:40 - 2:43</t>
+  </si>
+  <si>
+    <t>2:54 - 2:57</t>
+  </si>
+  <si>
+    <t>3:03 - 3:07</t>
+  </si>
+  <si>
+    <t>3:10 - 3:19</t>
+  </si>
+  <si>
+    <t>3:22 - 3:26</t>
+  </si>
+  <si>
+    <t>3:54 - 3:59</t>
+  </si>
+  <si>
+    <t>4:31 - 5:36</t>
+  </si>
+  <si>
+    <t>5:42 - 6:12</t>
+  </si>
+  <si>
+    <t>6:35 - 6:38</t>
+  </si>
+  <si>
+    <t>7:12 - 7:33</t>
+  </si>
+  <si>
+    <t>7:46 - 7:51</t>
+  </si>
+  <si>
+    <t>8:40 - 10:16</t>
+  </si>
+  <si>
+    <t>10:28 - 10:51</t>
+  </si>
+  <si>
+    <t>11:30 - 13:43</t>
+  </si>
+  <si>
+    <t>14:15 - 17:14</t>
+  </si>
+  <si>
+    <t>18:53 - 19:10</t>
+  </si>
+  <si>
+    <t>20:02 - 21:56</t>
+  </si>
+  <si>
+    <t>22:01 - 22:42</t>
+  </si>
+  <si>
+    <t>22:51 - 22:56</t>
+  </si>
+  <si>
+    <t>23:41 - 25:04</t>
+  </si>
+  <si>
+    <t>mouse jumped out</t>
+  </si>
+  <si>
+    <t>13:14 - 13:17</t>
+  </si>
+  <si>
+    <t>13:30 - 13:35</t>
+  </si>
+  <si>
+    <t>13:46 - 13:49</t>
+  </si>
+  <si>
+    <t>16:54 - 16:59</t>
+  </si>
+  <si>
+    <t>17:11 - 17:20</t>
+  </si>
+  <si>
+    <t>17:34 - 17:38</t>
+  </si>
+  <si>
+    <t>19:22 - 19:26</t>
+  </si>
+  <si>
+    <t>20:40 - 20:42</t>
+  </si>
+  <si>
+    <t>21:46 - 22:00</t>
+  </si>
+  <si>
+    <t>22:53 - 23:06</t>
+  </si>
+  <si>
+    <t>23:33 - 23:37</t>
+  </si>
+  <si>
+    <t>24:15 - 24:39</t>
+  </si>
+  <si>
+    <t>28:09 - 28:16</t>
+  </si>
+  <si>
+    <t>28:53 - 29:06</t>
+  </si>
+  <si>
+    <t>29:42 - 29:44</t>
+  </si>
+  <si>
+    <t>29:59 - 30:09</t>
+  </si>
+  <si>
+    <t>30:37 - 30:46</t>
+  </si>
+  <si>
+    <t>31:02 - 31:09</t>
+  </si>
+  <si>
+    <t>31:48 - 32:16</t>
+  </si>
+  <si>
+    <t>32:26 - 32:31</t>
+  </si>
+  <si>
+    <t>32:47 - 32:51</t>
+  </si>
+  <si>
+    <t>33:16 - 33:24</t>
+  </si>
+  <si>
+    <t>33:29 - 33:35</t>
+  </si>
+  <si>
+    <t>34:14 - 34:34</t>
+  </si>
+  <si>
+    <t>34:43 - 34:47</t>
+  </si>
+  <si>
+    <t>35:40 - 36:00</t>
+  </si>
+  <si>
+    <t>36:22 - 36:30</t>
+  </si>
+  <si>
+    <t>36:59 - 37:07</t>
+  </si>
+  <si>
+    <t>37:10 - 37:17</t>
+  </si>
+  <si>
+    <t>37:38 - 37:43</t>
+  </si>
+  <si>
+    <t>37:52 - 37:59</t>
+  </si>
+  <si>
+    <t>38:58 - 39:02</t>
+  </si>
+  <si>
+    <t>39:36 - 39:40</t>
+  </si>
+  <si>
+    <t>40:05 - 40:18</t>
+  </si>
+  <si>
+    <t>41:09 - 41:18</t>
+  </si>
+  <si>
+    <t>41:24 - 41:38</t>
+  </si>
+  <si>
+    <t>42:00 - 42:04</t>
+  </si>
+  <si>
+    <t>42:10 - 42:14</t>
+  </si>
+  <si>
+    <t>42:33 - 42:42</t>
+  </si>
+  <si>
+    <t>42:49 - 42:53</t>
+  </si>
+  <si>
+    <t>43:15 - 43:22</t>
+  </si>
+  <si>
+    <t>43:35 - 43:41</t>
+  </si>
+  <si>
+    <t>44:00 - 44:27</t>
+  </si>
+  <si>
+    <t>44:32 - 44:46</t>
+  </si>
+  <si>
+    <t>45:03 - 45:14</t>
+  </si>
+  <si>
+    <t>45:25 - 45:46</t>
+  </si>
+  <si>
+    <t>45:55 - 45:58</t>
+  </si>
+  <si>
+    <t>47:35 - 47:45</t>
+  </si>
+  <si>
+    <t>47:56 - 48:00</t>
+  </si>
+  <si>
+    <t>49:00 - 49:28</t>
+  </si>
+  <si>
+    <t>49:41 - 49:49</t>
+  </si>
+  <si>
+    <t>50:01 - 50:04</t>
+  </si>
+  <si>
+    <t>50:23 - 50:29</t>
+  </si>
+  <si>
+    <t>52:40 - 52:45</t>
+  </si>
+  <si>
+    <t>53:52 - 54:42</t>
+  </si>
+  <si>
+    <t>55:51 - 55:59</t>
+  </si>
+  <si>
+    <t>56:26 - 56:31</t>
+  </si>
+  <si>
+    <t>56:44 - 56:49</t>
+  </si>
+  <si>
+    <t>58:58 - 59:01</t>
+  </si>
+  <si>
+    <t>4:26 - 4:51</t>
+  </si>
+  <si>
+    <t>11:51 - 11:54</t>
+  </si>
+  <si>
+    <t>13:12 - 13:31</t>
+  </si>
+  <si>
+    <t>15:03 - 15:06</t>
+  </si>
+  <si>
+    <t>20:18 - 20:46</t>
+  </si>
+  <si>
+    <t>20:55 - 21:07</t>
+  </si>
+  <si>
+    <t>21:10 - 21:13</t>
+  </si>
+  <si>
+    <t>21:32 - 21:35</t>
+  </si>
+  <si>
+    <t>22:58 - 23:01</t>
+  </si>
+  <si>
+    <t>25:36 - 25:42</t>
+  </si>
+  <si>
+    <t>27:13 - 27:52</t>
+  </si>
+  <si>
+    <t>28:21 - 28:27</t>
+  </si>
+  <si>
+    <t>28:31 - 28:33</t>
+  </si>
+  <si>
+    <t>29:09 - 30:26</t>
+  </si>
+  <si>
+    <t>31:04 - 33:20</t>
+  </si>
+  <si>
+    <t>35:54 - 36:00</t>
+  </si>
+  <si>
+    <t>39:35 - 39:38</t>
+  </si>
+  <si>
+    <t>46:42 - 46:45</t>
+  </si>
+  <si>
+    <t>51:30 - 51:33</t>
+  </si>
+  <si>
+    <t>56:03 - 56:11</t>
+  </si>
+  <si>
+    <t>56:36 - 57:05</t>
+  </si>
+  <si>
+    <t>0:15 - 0:42</t>
+  </si>
+  <si>
+    <t>1:57 - 2:20</t>
+  </si>
+  <si>
+    <t>5:54 - 5:58</t>
+  </si>
+  <si>
+    <t>6:54 - 6:58</t>
+  </si>
+  <si>
+    <t>9:27 - 9:29</t>
+  </si>
+  <si>
+    <t>10:11 - 10:15</t>
+  </si>
+  <si>
+    <t>12:20 - 12:27</t>
+  </si>
+  <si>
+    <t>13:58 - 14:02</t>
+  </si>
+  <si>
+    <t>14:10 - 14:17</t>
+  </si>
+  <si>
+    <t>14:56 - 14:59</t>
+  </si>
+  <si>
+    <t>17:14 - 17:18</t>
+  </si>
+  <si>
+    <t>20:48 - 21:08</t>
+  </si>
+  <si>
+    <t>21:41 - 21:45</t>
+  </si>
+  <si>
+    <t>23:47 - 23:50</t>
+  </si>
+  <si>
+    <t>24:09 - 24:12</t>
+  </si>
+  <si>
+    <t>25:17 - 25:23</t>
+  </si>
+  <si>
+    <t>25:49 - 25:52</t>
+  </si>
+  <si>
+    <t>26:38 - 26:41</t>
+  </si>
+  <si>
+    <t>26:56 - 27:00</t>
+  </si>
+  <si>
+    <t>28:12 - 28:16</t>
+  </si>
+  <si>
+    <t>28:23 - 28:25</t>
+  </si>
+  <si>
+    <t>29:43 - 29:57</t>
+  </si>
+  <si>
+    <t>30:49 - 30:52</t>
+  </si>
+  <si>
+    <t>31:20 - 31:23</t>
+  </si>
+  <si>
+    <t>32:58 - 33:06</t>
+  </si>
+  <si>
+    <t>33:19 - 33:23</t>
+  </si>
+  <si>
+    <t>34:24 - 34:33</t>
+  </si>
+  <si>
+    <t>35:37 - 36:00</t>
+  </si>
+  <si>
+    <t>36:30 - 36:34</t>
+  </si>
+  <si>
+    <t>36:41 - 36:47</t>
+  </si>
+  <si>
+    <t>37:13 - 37:24</t>
+  </si>
+  <si>
+    <t>38:04 - 38:17</t>
+  </si>
+  <si>
+    <t>38:28 - 38:38</t>
+  </si>
+  <si>
+    <t>38:59 - 39:04</t>
+  </si>
+  <si>
+    <t>39:21 - 39:29</t>
+  </si>
+  <si>
+    <t>40:44 - 40:48</t>
+  </si>
+  <si>
+    <t>40:56 - 41:03</t>
+  </si>
+  <si>
+    <t>42:08 - 42:23</t>
+  </si>
+  <si>
+    <t>44:58 - 45:01</t>
+  </si>
+  <si>
+    <t>45:07 - 45:15</t>
+  </si>
+  <si>
+    <t>45:19 - 45:24</t>
+  </si>
+  <si>
+    <t>46:48 - 46:56</t>
+  </si>
+  <si>
+    <t>46:17 - 46:43</t>
+  </si>
+  <si>
+    <t>46:52 - 47:06</t>
+  </si>
+  <si>
+    <t>47:19 - 47:23</t>
+  </si>
+  <si>
+    <t>47:31 - 47:35</t>
+  </si>
+  <si>
+    <t>49:22 - 49:33</t>
+  </si>
+  <si>
+    <t>49:41 - 49:48</t>
+  </si>
+  <si>
+    <t>49:58 - 50:03</t>
+  </si>
+  <si>
+    <t>50:44 - 51:43</t>
+  </si>
+  <si>
+    <t>52:03 - 52:06</t>
+  </si>
+  <si>
+    <t>52:31 - 52:41</t>
+  </si>
+  <si>
+    <t>52:55 - 52:58</t>
+  </si>
+  <si>
+    <t>53:36 - 53:53</t>
+  </si>
+  <si>
+    <t>54:26 - 54:29</t>
+  </si>
+  <si>
+    <t>54:46 - 55:01</t>
+  </si>
+  <si>
+    <t>55:06 - 55:11</t>
+  </si>
+  <si>
+    <t>56:08 - 56:13</t>
+  </si>
+  <si>
+    <t>56:43 - 56:50</t>
+  </si>
+  <si>
+    <t>58:53 - 58:57</t>
+  </si>
+  <si>
+    <t>59:02 - 59:05</t>
+  </si>
+  <si>
+    <t>59:19 - 59:42</t>
+  </si>
+  <si>
+    <t>59:50 - 59:57</t>
+  </si>
+  <si>
+    <t>0:23 - 1:10</t>
+  </si>
+  <si>
+    <t>1:16 - 1:53</t>
+  </si>
+  <si>
+    <t>2:24 - 2:26</t>
+  </si>
+  <si>
+    <t>3:31 - 3:34</t>
+  </si>
+  <si>
+    <t>3:43 - 3:49</t>
+  </si>
+  <si>
+    <t>4:38 - 5:06</t>
+  </si>
+  <si>
+    <t>6:45 - 7:41</t>
+  </si>
+  <si>
+    <t>0:00 - 2:28</t>
+  </si>
+  <si>
+    <t>0:04 - 0:08</t>
+  </si>
+  <si>
+    <t>20:24 - 20:40</t>
+  </si>
+  <si>
+    <t>27:07 - 27:09</t>
+  </si>
+  <si>
+    <t>29:55 - 29:57</t>
+  </si>
+  <si>
+    <t>32:20 - 32:54</t>
+  </si>
+  <si>
+    <t>33:08 - 33:10</t>
+  </si>
+  <si>
+    <t>34:17 - 34:19</t>
+  </si>
+  <si>
+    <t>35:36 - 35:38</t>
+  </si>
+  <si>
+    <t>35:45 - 35:56</t>
+  </si>
+  <si>
+    <t>36:00 - 36:02</t>
+  </si>
+  <si>
+    <t>36:07 - 36:11</t>
+  </si>
+  <si>
+    <t>36:25 - 36:27</t>
+  </si>
+  <si>
+    <t>36:39 - 36:41</t>
+  </si>
+  <si>
+    <t>37:14 - 37:16</t>
+  </si>
+  <si>
+    <t>37:52 - 37:54</t>
+  </si>
+  <si>
+    <t>37:57 - 38:00</t>
+  </si>
+  <si>
+    <t>38:21 - 39:00</t>
+  </si>
+  <si>
+    <t>39:35 - 39:39</t>
+  </si>
+  <si>
+    <t>40:30 - 40:33</t>
+  </si>
+  <si>
+    <t>42:31 - 42:36</t>
+  </si>
+  <si>
+    <t>42:50 - 42:53</t>
+  </si>
+  <si>
+    <t>43:24 - 44:28</t>
+  </si>
+  <si>
+    <t>45:48 - 45:53</t>
+  </si>
+  <si>
+    <t>47:02 - 47:05</t>
+  </si>
+  <si>
+    <t>47:12 - 47:16</t>
+  </si>
+  <si>
+    <t>47:35 - 47:37</t>
+  </si>
+  <si>
+    <t>47:59 - 48:01</t>
+  </si>
+  <si>
+    <t>48:10 - 49:00</t>
+  </si>
+  <si>
+    <t>49:08 - 49:12</t>
+  </si>
+  <si>
+    <t>49:34 - 49:37</t>
+  </si>
+  <si>
+    <t>50:11 - 50:16</t>
+  </si>
+  <si>
+    <t>50:22 - 50:28</t>
+  </si>
+  <si>
+    <t>51:09 - 51:12</t>
+  </si>
+  <si>
+    <t>51:27 - 51:28</t>
+  </si>
+  <si>
+    <t>51:32 - 51:34</t>
+  </si>
+  <si>
+    <t>51:41 - 51:44</t>
+  </si>
+  <si>
+    <t>53:33 - 53:47</t>
+  </si>
+  <si>
+    <t>54:19 - 55:36</t>
+  </si>
+  <si>
+    <t>58:23 - 58:24</t>
+  </si>
+  <si>
+    <t>58:29 - 59:06</t>
+  </si>
+  <si>
+    <t>59:58 - 1:00:03</t>
+  </si>
+  <si>
+    <t>1:00:14 - 1:00:22</t>
+  </si>
+  <si>
+    <t>1:00:43 - 1:00:45</t>
+  </si>
+  <si>
+    <t>1:00:48 - 1:01:06</t>
+  </si>
+  <si>
+    <t>1:01:29 - 1:01:36</t>
+  </si>
+  <si>
+    <t>0:00 - 0:13</t>
+  </si>
+  <si>
+    <t>0:35 - 0:51</t>
+  </si>
+  <si>
+    <t>1:01 - 1:03</t>
+  </si>
+  <si>
+    <t>1:27 - 1:30</t>
+  </si>
+  <si>
+    <t>3:15 - 3:19</t>
+  </si>
+  <si>
+    <t>3:21 - 3:33</t>
+  </si>
+  <si>
+    <t>3:57 - 3:59</t>
+  </si>
+  <si>
+    <t>5:44 - 6:28</t>
+  </si>
+  <si>
+    <t>6:32 - 7:11</t>
+  </si>
+  <si>
+    <t>7:32 - 7:35</t>
+  </si>
+  <si>
+    <t>8:21 - 8:23</t>
+  </si>
+  <si>
+    <t>8:33 - 8:44</t>
+  </si>
+  <si>
+    <t>9:06 - 9:35</t>
+  </si>
+  <si>
+    <t>9:52 - 10:28</t>
+  </si>
+  <si>
+    <t>10:51 - 12:05</t>
+  </si>
+  <si>
+    <t>12:13 - 12:40</t>
+  </si>
+  <si>
+    <t>12:47 - 12:57</t>
+  </si>
+  <si>
+    <t>13:06 - 18:43</t>
+  </si>
+  <si>
+    <t>19:01 - 35:33</t>
+  </si>
+  <si>
+    <t>35:40 - 1:01:42</t>
+  </si>
+  <si>
+    <t>18:11 - 18:14</t>
+  </si>
+  <si>
+    <t>22:40 - 22:54</t>
+  </si>
+  <si>
+    <t>24:08 - 24:13</t>
+  </si>
+  <si>
+    <t>25:59 - 26:02</t>
+  </si>
+  <si>
+    <t>26:40 - 26:45</t>
+  </si>
+  <si>
+    <t>27:45 - 27:49</t>
+  </si>
+  <si>
+    <t>29:20 - 29:22</t>
+  </si>
+  <si>
+    <t>30:44 - 30:47</t>
+  </si>
+  <si>
+    <t>33:16 - 33:32</t>
+  </si>
+  <si>
+    <t>35:55 - 36:00</t>
+  </si>
+  <si>
+    <t>37:23 - 37:30</t>
+  </si>
+  <si>
+    <t>37:51 - 38:02</t>
+  </si>
+  <si>
+    <t>39:52 - 39:59</t>
+  </si>
+  <si>
+    <t>40:40 - 40:44</t>
+  </si>
+  <si>
+    <t>42:17 - 42:20</t>
+  </si>
+  <si>
+    <t>44:27 - 45:31</t>
+  </si>
+  <si>
+    <t>46:02 - 46:05</t>
+  </si>
+  <si>
+    <t>47:09 - 47:12</t>
+  </si>
+  <si>
+    <t>48:24 - 48:27</t>
+  </si>
+  <si>
+    <t>48:50 - 48:51</t>
+  </si>
+  <si>
+    <t>49:10 - 49:11</t>
+  </si>
+  <si>
+    <t>49:23 - 49:26</t>
+  </si>
+  <si>
+    <t>49:36 - 49:39</t>
+  </si>
+  <si>
+    <t>49:59 - 50:01</t>
+  </si>
+  <si>
+    <t>50:06 - 50:21</t>
+  </si>
+  <si>
+    <t>50:23 - 50:36</t>
+  </si>
+  <si>
+    <t>50:49 - 51:05</t>
+  </si>
+  <si>
+    <t>51:11 - 51:13</t>
+  </si>
+  <si>
+    <t>51:21 - 51:23</t>
+  </si>
+  <si>
+    <t>51:39 - 51:41</t>
+  </si>
+  <si>
+    <t>52:10 - 52:12</t>
+  </si>
+  <si>
+    <t>52:20 - 52:22</t>
+  </si>
+  <si>
+    <t>52:46 - 52:48</t>
+  </si>
+  <si>
+    <t>53:14 - 53:15</t>
+  </si>
+  <si>
+    <t>53:32 - 53:34</t>
+  </si>
+  <si>
+    <t>53:52 - 53:55</t>
+  </si>
+  <si>
+    <t>54:03 - 54:04</t>
+  </si>
+  <si>
+    <t>54:07 - 54:10</t>
+  </si>
+  <si>
+    <t>54:21 - 54:25</t>
+  </si>
+  <si>
+    <t>54:36 - 54:38</t>
+  </si>
+  <si>
+    <t>55:12 - 55:15</t>
+  </si>
+  <si>
+    <t>56:09 - 56:16</t>
+  </si>
+  <si>
+    <t>56:47 - 56:48</t>
+  </si>
+  <si>
+    <t>56:51 - 56:52</t>
+  </si>
+  <si>
+    <t>57:11 - 57:16</t>
+  </si>
+  <si>
+    <t>57:24 - 57:58</t>
+  </si>
+  <si>
+    <t>58:03 - 58:23</t>
+  </si>
+  <si>
+    <t>58:28 - 58:32</t>
+  </si>
+  <si>
+    <t>59:00 - 59:02</t>
+  </si>
+  <si>
+    <t>59:05 - 59:09</t>
+  </si>
+  <si>
+    <t>59:40 - 59:42</t>
+  </si>
+  <si>
+    <t>1:00:07 - 1:00:10</t>
+  </si>
+  <si>
+    <t>1:00:25 - 1:00:27</t>
+  </si>
+  <si>
+    <t>1:00:48 - 1:00:52</t>
+  </si>
+  <si>
+    <t>0:14 - 0:26</t>
+  </si>
+  <si>
+    <t>0:29 - 0:31</t>
+  </si>
+  <si>
+    <t>0:35 - 0:38</t>
+  </si>
+  <si>
+    <t>1:06 - 1:12</t>
+  </si>
+  <si>
+    <t>1:17 - 1:18</t>
+  </si>
+  <si>
+    <t>1:25 - 1:29</t>
+  </si>
+  <si>
+    <t>1:33 - 1:35</t>
+  </si>
+  <si>
+    <t>1:37 - 1:48</t>
+  </si>
+  <si>
+    <t>2:01 - 2:04</t>
+  </si>
+  <si>
+    <t>2:44 - 2:47</t>
+  </si>
+  <si>
+    <t>3:01 - 3:03</t>
+  </si>
+  <si>
+    <t>3:22 - 3:24</t>
+  </si>
+  <si>
+    <t>4:15 - 4:18</t>
+  </si>
+  <si>
+    <t>4:23 - 4:27</t>
+  </si>
+  <si>
+    <t>4:44 - 4:46</t>
+  </si>
+  <si>
+    <t>4:56 - 5:01</t>
+  </si>
+  <si>
+    <t>5:11 - 5:18</t>
+  </si>
+  <si>
+    <t>6:01 - 6:51</t>
+  </si>
+  <si>
+    <t>7:04 - 10:28</t>
+  </si>
+  <si>
+    <t>10:41 - 13:23</t>
+  </si>
+  <si>
+    <t>13:26 - 13:52</t>
+  </si>
+  <si>
+    <t>14:02 - 15:35</t>
+  </si>
+  <si>
+    <t>16:20 - 16:23</t>
+  </si>
+  <si>
+    <t>16:40 - 16:45</t>
+  </si>
+  <si>
+    <t>19:14 - 19:21</t>
+  </si>
+  <si>
+    <t>19:27 - 19:31</t>
+  </si>
+  <si>
+    <t>19:38 - 20:16</t>
+  </si>
+  <si>
+    <t>20:31 - 21:05</t>
+  </si>
+  <si>
+    <t>21:12 - 22:21</t>
+  </si>
+  <si>
+    <t>22:26 - 22:39</t>
+  </si>
+  <si>
+    <t>22:57 - 23:35</t>
+  </si>
+  <si>
+    <t>23:52 - 23:59</t>
+  </si>
+  <si>
+    <t>24:26 - 24:28</t>
+  </si>
+  <si>
+    <t>25:00 - 25:03</t>
+  </si>
+  <si>
+    <t>25:10 - 26:00</t>
+  </si>
+  <si>
+    <t>26:17 - 26:19</t>
+  </si>
+  <si>
+    <t>26:24 - 26:26</t>
+  </si>
+  <si>
+    <t>27:14 - 27:21</t>
+  </si>
+  <si>
+    <t>27:30 - 27:45</t>
+  </si>
+  <si>
+    <t>27:48 - 28:13</t>
+  </si>
+  <si>
+    <t>28:25 - 28:35</t>
+  </si>
+  <si>
+    <t>29:06 - 29:15</t>
+  </si>
+  <si>
+    <t>29:22 - 29:49</t>
+  </si>
+  <si>
+    <t>30:04 - 30:22</t>
+  </si>
+  <si>
+    <t>30:41 - 31:27</t>
+  </si>
+  <si>
+    <t>31:40 - 31:45</t>
+  </si>
+  <si>
+    <t>32:04 - 32:08</t>
+  </si>
+  <si>
+    <t>32:16 - 32:18</t>
+  </si>
+  <si>
+    <t>32:22 - 32:28</t>
+  </si>
+  <si>
+    <t>32:47 - 33:09</t>
+  </si>
+  <si>
+    <t>33:12 - 33:44</t>
+  </si>
+  <si>
+    <t>33:53 - 34:28</t>
+  </si>
+  <si>
+    <t>34:33 - 37:06</t>
+  </si>
+  <si>
+    <t>37:11 - 40:57</t>
+  </si>
+  <si>
+    <t>41:04 - 41:15</t>
+  </si>
+  <si>
+    <t>41:20 - 41:22</t>
+  </si>
+  <si>
+    <t>41:28 - 41:31</t>
+  </si>
+  <si>
+    <t>42:04 - 42:55</t>
+  </si>
+  <si>
+    <t>43:08 - 45:30</t>
+  </si>
+  <si>
+    <t>45:40 - 45:50</t>
+  </si>
+  <si>
+    <t>46:43 - 47:40</t>
+  </si>
+  <si>
+    <t>47:55 - 48:12</t>
+  </si>
+  <si>
+    <t>48:19 - 48:25</t>
+  </si>
+  <si>
+    <t>48:33 - 48:59</t>
+  </si>
+  <si>
+    <t>49:33 - 49:45</t>
+  </si>
+  <si>
+    <t>49:51 - 50:46</t>
+  </si>
+  <si>
+    <t>50:59 - 51:03</t>
+  </si>
+  <si>
+    <t>51:19 - 51:21</t>
+  </si>
+  <si>
+    <t>51:35 - 52:00</t>
+  </si>
+  <si>
+    <t>52:12 - 52:14</t>
+  </si>
+  <si>
+    <t>52:19 - 52:39</t>
+  </si>
+  <si>
+    <t>52:44 - 52:51</t>
+  </si>
+  <si>
+    <t>53:07 - 53:10</t>
+  </si>
+  <si>
+    <t>53:51 - 53:58</t>
+  </si>
+  <si>
+    <t>54:01 - 54:05</t>
+  </si>
+  <si>
+    <t>59:14 - 59:16</t>
+  </si>
+  <si>
+    <t>59:54 - 59:58</t>
   </si>
 </sst>
 </file>
@@ -1592,7 +3622,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m-d"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -1618,13 +3648,31 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <color rgb="FF222222"/>
+      <name val="&quot;Google Sans&quot;"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1E9F7"/>
+        <bgColor rgb="FFE1E9F7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1633,7 +3681,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1661,6 +3709,10 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1741,11 +3793,103 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing26.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing27.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing28.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing29.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing30.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing31.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing32.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing33.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing34.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing35.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing36.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing37.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing38.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing39.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing40.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing41.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing42.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing43.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing44.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing45.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing46.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing47.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing48.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1767,6 +3911,10 @@
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3900,6 +6048,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="15.56"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
@@ -3910,6 +6061,406 @@
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C6" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C7" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C9" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C16" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C18" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C21" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C22" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C23" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C25" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C27" s="7">
+        <v>46024.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C28" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C31" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C33" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C35" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C36" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C37" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C38" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C39" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C41" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C42" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C43" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C44" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C45" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C46" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C47" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C48" s="7">
+        <v>46025.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C49" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C50" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C51" s="7">
+        <v>46058.0</v>
       </c>
     </row>
   </sheetData>
@@ -3937,7 +6488,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="C2" s="1">
         <v>2.0</v>
@@ -3945,7 +6496,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>401</v>
+        <v>451</v>
       </c>
       <c r="C3" s="1">
         <v>2.0</v>
@@ -3953,7 +6504,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>402</v>
+        <v>452</v>
       </c>
       <c r="C4" s="1">
         <v>2.0</v>
@@ -3961,7 +6512,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>403</v>
+        <v>453</v>
       </c>
       <c r="C5" s="1">
         <v>2.0</v>
@@ -3969,7 +6520,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>404</v>
+        <v>454</v>
       </c>
       <c r="C6" s="1">
         <v>2.0</v>
@@ -3977,7 +6528,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>405</v>
+        <v>455</v>
       </c>
       <c r="C7" s="1">
         <v>2.0</v>
@@ -3985,7 +6536,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>406</v>
+        <v>456</v>
       </c>
       <c r="C8" s="1">
         <v>2.0</v>
@@ -3993,7 +6544,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="C9" s="1">
         <v>2.0</v>
@@ -4001,7 +6552,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>408</v>
+        <v>458</v>
       </c>
       <c r="C10" s="1">
         <v>2.0</v>
@@ -4009,7 +6560,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>409</v>
+        <v>459</v>
       </c>
       <c r="C11" s="1">
         <v>2.0</v>
@@ -4017,7 +6568,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="C12" s="1">
         <v>2.0</v>
@@ -4025,7 +6576,7 @@
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>411</v>
+        <v>461</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="10">
@@ -4034,7 +6585,7 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>412</v>
+        <v>462</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="10">
@@ -4043,7 +6594,7 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>413</v>
+        <v>463</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="10">
@@ -4052,7 +6603,7 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>414</v>
+        <v>464</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="10">
@@ -4061,7 +6612,7 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>415</v>
+        <v>465</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="10">
@@ -4070,7 +6621,7 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="10">
@@ -4079,7 +6630,7 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>417</v>
+        <v>467</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="10">
@@ -4088,7 +6639,7 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>418</v>
+        <v>468</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="10">
@@ -4097,7 +6648,7 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>419</v>
+        <v>469</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="10">
@@ -4106,7 +6657,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="C22" s="10">
         <v>2.0</v>
@@ -4114,7 +6665,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="C23" s="10">
         <v>2.0</v>
@@ -4122,7 +6673,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>422</v>
+        <v>472</v>
       </c>
       <c r="C24" s="10">
         <v>2.0</v>
@@ -4130,7 +6681,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>423</v>
+        <v>473</v>
       </c>
       <c r="C25" s="10">
         <v>2.0</v>
@@ -4138,7 +6689,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="C26" s="10">
         <v>2.0</v>
@@ -4146,7 +6697,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>425</v>
+        <v>475</v>
       </c>
       <c r="C27" s="10">
         <v>2.0</v>
@@ -4154,7 +6705,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>426</v>
+        <v>476</v>
       </c>
       <c r="C28" s="10">
         <v>2.0</v>
@@ -4162,7 +6713,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="C29" s="10">
         <v>2.0</v>
@@ -4170,7 +6721,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>428</v>
+        <v>478</v>
       </c>
       <c r="C30" s="10">
         <v>2.0</v>
@@ -4178,7 +6729,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>429</v>
+        <v>479</v>
       </c>
       <c r="C31" s="10">
         <v>2.0</v>
@@ -4186,7 +6737,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>430</v>
+        <v>480</v>
       </c>
       <c r="C32" s="10">
         <v>2.0</v>
@@ -4203,6 +6754,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="13.22"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
@@ -4213,6 +6767,286 @@
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C3" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C7" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C9" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C12" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C16" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C18" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C19" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C20" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C22" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C23" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C24" s="7">
+        <v>46025.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C25" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C26" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C27" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C28" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C30" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C32" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C33" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C34" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C35" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C36" s="7">
+        <v>46056.0</v>
       </c>
     </row>
   </sheetData>
@@ -7339,7 +10173,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>431</v>
+        <v>516</v>
       </c>
       <c r="C2" s="1">
         <v>2.0</v>
@@ -7347,7 +10181,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>432</v>
+        <v>517</v>
       </c>
       <c r="C3" s="1">
         <v>2.0</v>
@@ -7355,7 +10189,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>433</v>
+        <v>518</v>
       </c>
       <c r="C4" s="1">
         <v>2.0</v>
@@ -7363,7 +10197,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>434</v>
+        <v>519</v>
       </c>
       <c r="C5" s="1">
         <v>2.0</v>
@@ -7371,7 +10205,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>435</v>
+        <v>520</v>
       </c>
       <c r="C6" s="7">
         <v>46056.0</v>
@@ -7379,7 +10213,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>436</v>
+        <v>521</v>
       </c>
       <c r="C7" s="7">
         <v>46056.0</v>
@@ -7387,7 +10221,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>437</v>
+        <v>522</v>
       </c>
       <c r="C8" s="1">
         <v>2.0</v>
@@ -7395,7 +10229,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>438</v>
+        <v>523</v>
       </c>
       <c r="C9" s="1">
         <v>2.0</v>
@@ -7403,7 +10237,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>439</v>
+        <v>524</v>
       </c>
       <c r="C10" s="1">
         <v>2.0</v>
@@ -7411,7 +10245,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>440</v>
+        <v>525</v>
       </c>
       <c r="C11" s="1">
         <v>2.0</v>
@@ -7419,7 +10253,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>441</v>
+        <v>526</v>
       </c>
       <c r="C12" s="1">
         <v>2.0</v>
@@ -7427,7 +10261,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>442</v>
+        <v>527</v>
       </c>
       <c r="C13" s="1">
         <v>2.0</v>
@@ -7435,7 +10269,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>443</v>
+        <v>528</v>
       </c>
       <c r="C14" s="1">
         <v>2.0</v>
@@ -7443,7 +10277,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>444</v>
+        <v>529</v>
       </c>
       <c r="C15" s="1">
         <v>2.0</v>
@@ -7451,7 +10285,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>445</v>
+        <v>530</v>
       </c>
       <c r="C16" s="1">
         <v>2.0</v>
@@ -7459,7 +10293,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>446</v>
+        <v>531</v>
       </c>
       <c r="C17" s="1">
         <v>2.0</v>
@@ -7467,7 +10301,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>447</v>
+        <v>532</v>
       </c>
       <c r="C18" s="1">
         <v>2.0</v>
@@ -7475,7 +10309,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>448</v>
+        <v>533</v>
       </c>
       <c r="C19" s="1">
         <v>2.0</v>
@@ -7483,7 +10317,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>449</v>
+        <v>534</v>
       </c>
       <c r="C20" s="1">
         <v>2.0</v>
@@ -7491,7 +10325,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>450</v>
+        <v>535</v>
       </c>
       <c r="C21" s="1">
         <v>2.0</v>
@@ -7499,7 +10333,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>451</v>
+        <v>536</v>
       </c>
       <c r="C22" s="1">
         <v>2.0</v>
@@ -7507,7 +10341,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>452</v>
+        <v>537</v>
       </c>
       <c r="C23" s="1">
         <v>2.0</v>
@@ -7515,7 +10349,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>453</v>
+        <v>538</v>
       </c>
       <c r="C24" s="1">
         <v>2.0</v>
@@ -7523,7 +10357,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>454</v>
+        <v>539</v>
       </c>
       <c r="C25" s="1">
         <v>2.0</v>
@@ -7531,7 +10365,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>455</v>
+        <v>540</v>
       </c>
       <c r="C26" s="1">
         <v>2.0</v>
@@ -7539,7 +10373,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>456</v>
+        <v>541</v>
       </c>
       <c r="C27" s="1">
         <v>2.0</v>
@@ -7547,7 +10381,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>457</v>
+        <v>542</v>
       </c>
       <c r="C28" s="1">
         <v>2.0</v>
@@ -7555,7 +10389,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>458</v>
+        <v>543</v>
       </c>
       <c r="C29" s="1">
         <v>2.0</v>
@@ -7563,7 +10397,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>459</v>
+        <v>544</v>
       </c>
       <c r="C30" s="1">
         <v>2.0</v>
@@ -7571,7 +10405,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>460</v>
+        <v>545</v>
       </c>
       <c r="C31" s="1">
         <v>2.0</v>
@@ -7579,7 +10413,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>461</v>
+        <v>546</v>
       </c>
       <c r="C32" s="1">
         <v>2.0</v>
@@ -7587,7 +10421,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>462</v>
+        <v>547</v>
       </c>
       <c r="C33" s="1">
         <v>2.0</v>
@@ -7616,6 +10450,278 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C3" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46027.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C9" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C11" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C15" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C16" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46086.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="C18" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C20" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C21" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C22" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C23" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C24" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C25" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C26" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C27" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="C28" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C29" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C30" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="C31" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C32" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C33" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C34" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C35" s="7">
+        <v>46057.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -7641,7 +10747,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>463</v>
+        <v>582</v>
       </c>
       <c r="C2" s="7">
         <v>46024.0</v>
@@ -7649,7 +10755,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>464</v>
+        <v>583</v>
       </c>
       <c r="C3" s="1">
         <v>2.0</v>
@@ -7657,7 +10763,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>465</v>
+        <v>584</v>
       </c>
       <c r="C4" s="1">
         <v>2.0</v>
@@ -7665,7 +10771,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>466</v>
+        <v>585</v>
       </c>
       <c r="C5" s="1">
         <v>2.0</v>
@@ -7673,7 +10779,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>467</v>
+        <v>586</v>
       </c>
       <c r="C6" s="1">
         <v>2.0</v>
@@ -7681,7 +10787,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>468</v>
+        <v>587</v>
       </c>
       <c r="C7" s="1">
         <v>2.0</v>
@@ -7689,7 +10795,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>469</v>
+        <v>588</v>
       </c>
       <c r="C8" s="1">
         <v>2.0</v>
@@ -7697,7 +10803,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>470</v>
+        <v>589</v>
       </c>
       <c r="C9" s="1">
         <v>2.0</v>
@@ -7705,7 +10811,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>471</v>
+        <v>590</v>
       </c>
       <c r="C10" s="1">
         <v>2.0</v>
@@ -7713,7 +10819,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>472</v>
+        <v>591</v>
       </c>
       <c r="C11" s="1">
         <v>2.0</v>
@@ -7721,7 +10827,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>473</v>
+        <v>592</v>
       </c>
       <c r="C12" s="1">
         <v>2.0</v>
@@ -7729,7 +10835,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>474</v>
+        <v>593</v>
       </c>
       <c r="C13" s="1">
         <v>2.0</v>
@@ -7737,7 +10843,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>475</v>
+        <v>594</v>
       </c>
       <c r="C14" s="1">
         <v>2.0</v>
@@ -7745,7 +10851,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>476</v>
+        <v>595</v>
       </c>
       <c r="C15" s="1">
         <v>2.0</v>
@@ -7753,7 +10859,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>477</v>
+        <v>596</v>
       </c>
       <c r="C16" s="1">
         <v>2.0</v>
@@ -7761,7 +10867,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>478</v>
+        <v>597</v>
       </c>
       <c r="C17" s="1">
         <v>2.0</v>
@@ -7769,7 +10875,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>479</v>
+        <v>598</v>
       </c>
       <c r="C18" s="1">
         <v>2.0</v>
@@ -7777,7 +10883,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>480</v>
+        <v>599</v>
       </c>
       <c r="C19" s="7">
         <v>46024.0</v>
@@ -7785,7 +10891,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>481</v>
+        <v>600</v>
       </c>
       <c r="C20" s="1">
         <v>2.0</v>
@@ -7793,7 +10899,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>482</v>
+        <v>601</v>
       </c>
       <c r="C21" s="1">
         <v>2.0</v>
@@ -7801,7 +10907,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>483</v>
+        <v>602</v>
       </c>
       <c r="C22" s="1">
         <v>2.0</v>
@@ -7809,7 +10915,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>484</v>
+        <v>603</v>
       </c>
       <c r="C23" s="1">
         <v>2.0</v>
@@ -7817,7 +10923,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>485</v>
+        <v>604</v>
       </c>
       <c r="C24" s="1">
         <v>2.0</v>
@@ -7825,7 +10931,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>486</v>
+        <v>605</v>
       </c>
       <c r="C25" s="1">
         <v>2.0</v>
@@ -7833,7 +10939,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>487</v>
+        <v>606</v>
       </c>
       <c r="C26" s="1">
         <v>2.0</v>
@@ -7841,7 +10947,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>488</v>
+        <v>607</v>
       </c>
       <c r="C27" s="1">
         <v>2.0</v>
@@ -7849,7 +10955,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>489</v>
+        <v>608</v>
       </c>
       <c r="C28" s="1">
         <v>2.0</v>
@@ -7878,6 +10984,494 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="C18" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="C26" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="C30" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C31" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="C32" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C33" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="C34" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C44" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="C48" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="C50" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C52" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="C53" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="C54" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C55" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="C56" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C58" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="C59" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="C60" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C61" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C62" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -7903,7 +11497,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>490</v>
+        <v>670</v>
       </c>
       <c r="C2" s="1">
         <v>2.0</v>
@@ -7911,7 +11505,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>491</v>
+        <v>671</v>
       </c>
       <c r="C3" s="1">
         <v>2.0</v>
@@ -7919,7 +11513,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>492</v>
+        <v>672</v>
       </c>
       <c r="C4" s="7">
         <v>46056.0</v>
@@ -7927,7 +11521,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>493</v>
+        <v>673</v>
       </c>
       <c r="C5" s="1">
         <v>2.0</v>
@@ -7935,7 +11529,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>494</v>
+        <v>674</v>
       </c>
       <c r="C6" s="1">
         <v>2.0</v>
@@ -7943,7 +11537,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>495</v>
+        <v>675</v>
       </c>
       <c r="C7" s="1">
         <v>2.0</v>
@@ -7951,7 +11545,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>496</v>
+        <v>676</v>
       </c>
       <c r="C8" s="1">
         <v>2.0</v>
@@ -7959,7 +11553,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>497</v>
+        <v>677</v>
       </c>
       <c r="C9" s="1">
         <v>2.0</v>
@@ -7967,7 +11561,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>498</v>
+        <v>678</v>
       </c>
       <c r="C10" s="1">
         <v>2.0</v>
@@ -7975,7 +11569,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>499</v>
+        <v>679</v>
       </c>
       <c r="C11" s="1">
         <v>2.0</v>
@@ -7983,7 +11577,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>500</v>
+        <v>680</v>
       </c>
       <c r="C12" s="1">
         <v>2.0</v>
@@ -7991,7 +11585,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>501</v>
+        <v>681</v>
       </c>
       <c r="C13" s="1">
         <v>2.0</v>
@@ -7999,7 +11593,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>502</v>
+        <v>682</v>
       </c>
       <c r="C14" s="1">
         <v>2.0</v>
@@ -8007,7 +11601,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>503</v>
+        <v>683</v>
       </c>
       <c r="C15" s="1">
         <v>2.0</v>
@@ -8015,7 +11609,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>504</v>
+        <v>684</v>
       </c>
       <c r="C16" s="1">
         <v>2.0</v>
@@ -8023,7 +11617,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>505</v>
+        <v>685</v>
       </c>
       <c r="C17" s="1">
         <v>2.0</v>
@@ -8031,7 +11625,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>506</v>
+        <v>686</v>
       </c>
       <c r="C18" s="1">
         <v>2.0</v>
@@ -8039,7 +11633,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>507</v>
+        <v>687</v>
       </c>
       <c r="C19" s="1">
         <v>2.0</v>
@@ -8047,7 +11641,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>508</v>
+        <v>688</v>
       </c>
       <c r="C20" s="1">
         <v>2.0</v>
@@ -8055,7 +11649,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>509</v>
+        <v>689</v>
       </c>
       <c r="C21" s="1">
         <v>2.0</v>
@@ -8063,7 +11657,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>510</v>
+        <v>690</v>
       </c>
       <c r="C22" s="1">
         <v>2.0</v>
@@ -8071,7 +11665,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>511</v>
+        <v>691</v>
       </c>
       <c r="C23" s="1">
         <v>2.0</v>
@@ -8079,7 +11673,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>512</v>
+        <v>692</v>
       </c>
       <c r="C24" s="1">
         <v>2.0</v>
@@ -8087,7 +11681,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>513</v>
+        <v>693</v>
       </c>
       <c r="C25" s="1">
         <v>2.0</v>
@@ -8095,7 +11689,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>514</v>
+        <v>694</v>
       </c>
       <c r="C26" s="1">
         <v>2.0</v>
@@ -8103,17 +11697,59 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>515</v>
+        <v>695</v>
       </c>
       <c r="C27" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="1"/>
+      <c r="A28" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="29">
-      <c r="C29" s="1"/>
+      <c r="A29" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -8126,6 +11762,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="13.22"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
@@ -8136,6 +11775,1195 @@
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="C9" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="C18" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="C19" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C20" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C37" s="7">
+        <v>46027.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="C38" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="C49" s="7">
+        <v>46027.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="13.67"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="13.11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="14.22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="C5" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="C23" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="16.33"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="C3" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="C12" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="C19" s="7">
+        <v>46024.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="C20" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="C22" s="7">
+        <v>46027.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="C23" s="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="C25" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="1" t="s">
+        <v>837</v>
       </c>
     </row>
   </sheetData>
@@ -8168,7 +12996,7 @@
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -11240,6 +16068,1396 @@
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="C50" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="C52" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="C53" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="C54" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="C55" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="C56" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="C58" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="C59" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="C60" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C6" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="C12" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="C13" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="C16" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="C44" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="C45" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="C46" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="C47" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="C50" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="C52" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="C53" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="C54" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="C55" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="C56" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="C58" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="C59" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="C60" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="C61" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="C62" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="C63" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="C64" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="16.22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="C3" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="C7" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="1" t="s">
+        <v>837</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -14401,6 +20619,1737 @@
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="15.0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="C3" s="7">
+        <v>46024.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C18" s="7">
+        <v>46024.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C23" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C29" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="12.44"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C11" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C16" s="7">
+        <v>46024.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46024.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C19" s="7">
+        <v>46027.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C20" s="7">
+        <v>46027.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C21" s="7">
+        <v>46027.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="15.0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C18" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C20" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C25" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C28" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C30" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C39" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C50" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C52" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C53" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C54" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C55" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C56" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C20" s="7">
+        <v>46024.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C21" s="7">
+        <v>46024.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C22" s="7">
+        <v>46025.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C23" s="7">
+        <v>46024.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C26" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C28" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C31" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C33" s="7">
+        <v>46025.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C34" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C35" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C36" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C37" s="7">
+        <v>46025.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C38" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C39" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C44" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C45" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C46" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C47" s="7">
+        <v>46025.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C48" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C49" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C50" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C51" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C52" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C53" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C54" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C55" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C56" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C57" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C58" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C59" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C60" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C61" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C62" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C63" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C64" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C65" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C67" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C68" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C69" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C70" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C71" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C72" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C73" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C74" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C75" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C76" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C77" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C78" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C79" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C80" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/data/seizure_stage.xlsx
+++ b/data/seizure_stage.xlsx
@@ -51,6 +51,10 @@
     <sheet state="visible" name="010626F1_B" sheetId="46" r:id="rId50"/>
     <sheet state="visible" name="010626F2" sheetId="47" r:id="rId51"/>
     <sheet state="visible" name="010626F2_B" sheetId="48" r:id="rId52"/>
+    <sheet state="visible" name="010626M1" sheetId="49" r:id="rId53"/>
+    <sheet state="visible" name="010626M1_B" sheetId="50" r:id="rId54"/>
+    <sheet state="visible" name="010626M2" sheetId="51" r:id="rId55"/>
+    <sheet state="visible" name="010626M2_B" sheetId="52" r:id="rId56"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -58,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="1185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="1631">
   <si>
     <t>Stage</t>
   </si>
@@ -2787,7 +2791,7 @@
     <t>28:21 - 28:27</t>
   </si>
   <si>
-    <t>28:31 - 28:33</t>
+    <t>28:33 - 28:35</t>
   </si>
   <si>
     <t>29:09 - 30:26</t>
@@ -3027,6 +3031,930 @@
     <t>0:00 - 2:28</t>
   </si>
   <si>
+    <t>2:33 - 6:14</t>
+  </si>
+  <si>
+    <t>6:27 - 8:45</t>
+  </si>
+  <si>
+    <t>9:00 - 10:45</t>
+  </si>
+  <si>
+    <t>11:15 - 11:55</t>
+  </si>
+  <si>
+    <t>12:05 - 30:33</t>
+  </si>
+  <si>
+    <t>1:46 - 2:27</t>
+  </si>
+  <si>
+    <t>8:14 - 8:18</t>
+  </si>
+  <si>
+    <t>9:17 - 9:21</t>
+  </si>
+  <si>
+    <t>13:13 - 13:17</t>
+  </si>
+  <si>
+    <t>14:10 - 14:16</t>
+  </si>
+  <si>
+    <t>14:39 - 14:42</t>
+  </si>
+  <si>
+    <t>15:02 - 15:06</t>
+  </si>
+  <si>
+    <t>15:26 - 15:29</t>
+  </si>
+  <si>
+    <t>16:42 - 16:44</t>
+  </si>
+  <si>
+    <t>16:52 - 16:54</t>
+  </si>
+  <si>
+    <t>17:24 - 17:31</t>
+  </si>
+  <si>
+    <t>18:04 - 18:09</t>
+  </si>
+  <si>
+    <t>18:22 - 19:36</t>
+  </si>
+  <si>
+    <t>19:57 - 20:06</t>
+  </si>
+  <si>
+    <t>23:05 - 23:07</t>
+  </si>
+  <si>
+    <t>23:53 - 23:56</t>
+  </si>
+  <si>
+    <t>24:02 - 24:04</t>
+  </si>
+  <si>
+    <t>24:28 - 24:32</t>
+  </si>
+  <si>
+    <t>24:49 - 24:52</t>
+  </si>
+  <si>
+    <t>25:27 - 25:49</t>
+  </si>
+  <si>
+    <t>26:13 - 26:22</t>
+  </si>
+  <si>
+    <t>26:45 - 26:48</t>
+  </si>
+  <si>
+    <t>29:12 - 29:14</t>
+  </si>
+  <si>
+    <t>29:34 - 31:14</t>
+  </si>
+  <si>
+    <t>31:28 - 31:31</t>
+  </si>
+  <si>
+    <t>31:57 - 32:00</t>
+  </si>
+  <si>
+    <t>38:32 - 39:09</t>
+  </si>
+  <si>
+    <t>39:27 - 39:29</t>
+  </si>
+  <si>
+    <t>47:52 - 47:56</t>
+  </si>
+  <si>
+    <t>48:24 - 48:32</t>
+  </si>
+  <si>
+    <t>52:15 - 52:19</t>
+  </si>
+  <si>
+    <t>53:51 - 54:00</t>
+  </si>
+  <si>
+    <t>55:26 - 55:40</t>
+  </si>
+  <si>
+    <t>58:55 - 59:00</t>
+  </si>
+  <si>
+    <t>59:13 - 59:21</t>
+  </si>
+  <si>
+    <t>59:30 - 59:33</t>
+  </si>
+  <si>
+    <t>3:26 - 4:00</t>
+  </si>
+  <si>
+    <t>11:05 - 11:45</t>
+  </si>
+  <si>
+    <t>16:45 - 16:48</t>
+  </si>
+  <si>
+    <t>17:40 - 18:45</t>
+  </si>
+  <si>
+    <t>22:19 - 22:22</t>
+  </si>
+  <si>
+    <t>24:00 - 24:07</t>
+  </si>
+  <si>
+    <t>24:17 - 24:41</t>
+  </si>
+  <si>
+    <t>26:28 - 26:59</t>
+  </si>
+  <si>
+    <t>30:13 - 31:45</t>
+  </si>
+  <si>
+    <t>33:23 - 33:29</t>
+  </si>
+  <si>
+    <t>35:03 - 35:05</t>
+  </si>
+  <si>
+    <t>35:13 - 35:15</t>
+  </si>
+  <si>
+    <t>38:01 - 38:28</t>
+  </si>
+  <si>
+    <t>39:13 - 39:21</t>
+  </si>
+  <si>
+    <t>39:50 - 40:28</t>
+  </si>
+  <si>
+    <t>41:07 - 41:12</t>
+  </si>
+  <si>
+    <t>42:01 - 42:05</t>
+  </si>
+  <si>
+    <t>42:53 - 43:47</t>
+  </si>
+  <si>
+    <t>43:56 - 44:26</t>
+  </si>
+  <si>
+    <t>45:38 - 45:49</t>
+  </si>
+  <si>
+    <t>46:13 - 46:23</t>
+  </si>
+  <si>
+    <t>47:51 - 48:23</t>
+  </si>
+  <si>
+    <t>48:59 - 49:02</t>
+  </si>
+  <si>
+    <t>50:00 - 50:55</t>
+  </si>
+  <si>
+    <t>51:45 - 52:58</t>
+  </si>
+  <si>
+    <t>53:11 - 53:25</t>
+  </si>
+  <si>
+    <t>58:40 - 58:55</t>
+  </si>
+  <si>
+    <t>58:18 - 58:23</t>
+  </si>
+  <si>
+    <t>58:45 - 59:55</t>
+  </si>
+  <si>
+    <t>12:51 - 13:00</t>
+  </si>
+  <si>
+    <t>20:04 - 20:22</t>
+  </si>
+  <si>
+    <t>23:22 - 23:41</t>
+  </si>
+  <si>
+    <t>24:56 - 25:17</t>
+  </si>
+  <si>
+    <t>27:50 - 27:52</t>
+  </si>
+  <si>
+    <t>29:29 - 29:53</t>
+  </si>
+  <si>
+    <t>30:51 - 31:14</t>
+  </si>
+  <si>
+    <t>32:07 - 32:11</t>
+  </si>
+  <si>
+    <t>33:49 - 34:16</t>
+  </si>
+  <si>
+    <t>34:25 - 34:32</t>
+  </si>
+  <si>
+    <t>36:08 - 36:12</t>
+  </si>
+  <si>
+    <t>37:33 - 37:36</t>
+  </si>
+  <si>
+    <t>37:47 - 37:50</t>
+  </si>
+  <si>
+    <t>37:59 - 38:20</t>
+  </si>
+  <si>
+    <t>38:57 - 39:02</t>
+  </si>
+  <si>
+    <t>39:37 - 39:40</t>
+  </si>
+  <si>
+    <t>40:42 - 41:25</t>
+  </si>
+  <si>
+    <t>41:30 - 41:41</t>
+  </si>
+  <si>
+    <t>43:17 - 43:20</t>
+  </si>
+  <si>
+    <t>44:52 - 45:54</t>
+  </si>
+  <si>
+    <t>47:38 - 47:47</t>
+  </si>
+  <si>
+    <t>48:13 - 48:16</t>
+  </si>
+  <si>
+    <t>49:23 - 49:27</t>
+  </si>
+  <si>
+    <t>49:59 - 50:06</t>
+  </si>
+  <si>
+    <t>50:49 - 51:05</t>
+  </si>
+  <si>
+    <t>51:18 - 52:05</t>
+  </si>
+  <si>
+    <t>52:13 - 52:29</t>
+  </si>
+  <si>
+    <t>52:57 - 53:01</t>
+  </si>
+  <si>
+    <t>53:29 - 53:45</t>
+  </si>
+  <si>
+    <t>54:17 - 54:27</t>
+  </si>
+  <si>
+    <t>54:38 - 54:41</t>
+  </si>
+  <si>
+    <t>54:44 - 54:53</t>
+  </si>
+  <si>
+    <t>55:12 - 55:27</t>
+  </si>
+  <si>
+    <t>55:56 - 56:02</t>
+  </si>
+  <si>
+    <t>56:19 - 56:25</t>
+  </si>
+  <si>
+    <t>56:39 - 56:46</t>
+  </si>
+  <si>
+    <t>57:11 - 57:23</t>
+  </si>
+  <si>
+    <t>57:34 - 57:39</t>
+  </si>
+  <si>
+    <t>57:50 - 57:54</t>
+  </si>
+  <si>
+    <t>58:01 - 58:12</t>
+  </si>
+  <si>
+    <t>58:37 - 59:14</t>
+  </si>
+  <si>
+    <t>59:27 - 59:50</t>
+  </si>
+  <si>
+    <t>0:21 - 1:05</t>
+  </si>
+  <si>
+    <t>1:19 - 2:23</t>
+  </si>
+  <si>
+    <t>2:35 - 6:01</t>
+  </si>
+  <si>
+    <t>7:24 - 7:32</t>
+  </si>
+  <si>
+    <t>8:11 - 8:16</t>
+  </si>
+  <si>
+    <t>9:01 - 9:11</t>
+  </si>
+  <si>
+    <t>9:37 - 9:46</t>
+  </si>
+  <si>
+    <t>10:18 - 11:58</t>
+  </si>
+  <si>
+    <t>12:04 - 12:11</t>
+  </si>
+  <si>
+    <t>12:19 - 12:30</t>
+  </si>
+  <si>
+    <t>12:58 - 13:07</t>
+  </si>
+  <si>
+    <t>13:19 - 14:43</t>
+  </si>
+  <si>
+    <t>14:54 - 30:20</t>
+  </si>
+  <si>
+    <t>33:35 - 34:55</t>
+  </si>
+  <si>
+    <t>35:25 - 35:35</t>
+  </si>
+  <si>
+    <t>35:48 - 37:29</t>
+  </si>
+  <si>
+    <t>39:41 - 40:14</t>
+  </si>
+  <si>
+    <t>40:28 - 44:37</t>
+  </si>
+  <si>
+    <t>12:39 - 12:43</t>
+  </si>
+  <si>
+    <t>14:22 - 14:35</t>
+  </si>
+  <si>
+    <t>30:33 - 30:48</t>
+  </si>
+  <si>
+    <t>31:56 - 31:59</t>
+  </si>
+  <si>
+    <t>35:28 - 35:53</t>
+  </si>
+  <si>
+    <t>36:31 - 36:33</t>
+  </si>
+  <si>
+    <t>38:41 - 38:44</t>
+  </si>
+  <si>
+    <t>39:05 - 39:12</t>
+  </si>
+  <si>
+    <t>39:25 - 39:33</t>
+  </si>
+  <si>
+    <t>39:47 - 39:51</t>
+  </si>
+  <si>
+    <t>40:29 - 40:34</t>
+  </si>
+  <si>
+    <t>41:58 - 42:01</t>
+  </si>
+  <si>
+    <t>42:32 - 42:35</t>
+  </si>
+  <si>
+    <t>43:11 - 43:18</t>
+  </si>
+  <si>
+    <t>44:20 - 44:32</t>
+  </si>
+  <si>
+    <t>45:07 - 45:11</t>
+  </si>
+  <si>
+    <t>46:11 - 46:16</t>
+  </si>
+  <si>
+    <t>46:52 - 46:59</t>
+  </si>
+  <si>
+    <t>49:22 - 49:25</t>
+  </si>
+  <si>
+    <t>50:02 - 50:16</t>
+  </si>
+  <si>
+    <t>50:51 - 51:53</t>
+  </si>
+  <si>
+    <t>52:29 - 52:50</t>
+  </si>
+  <si>
+    <t>54:13 - 55:02</t>
+  </si>
+  <si>
+    <t>55:09 - 55:13</t>
+  </si>
+  <si>
+    <t>55:43 - 55:55</t>
+  </si>
+  <si>
+    <t>56:21 - 56:46</t>
+  </si>
+  <si>
+    <t>56:59 - 57:05</t>
+  </si>
+  <si>
+    <t>57:13 - 57:18</t>
+  </si>
+  <si>
+    <t>57:26 - 57:32</t>
+  </si>
+  <si>
+    <t>58:20 - 58:25</t>
+  </si>
+  <si>
+    <t>58:32 - 58:40</t>
+  </si>
+  <si>
+    <t>58:55 - 58:58</t>
+  </si>
+  <si>
+    <t>59:25 - 59:29</t>
+  </si>
+  <si>
+    <t>59:50 - 59:53</t>
+  </si>
+  <si>
+    <t>0:03 - 0:35</t>
+  </si>
+  <si>
+    <t>0:52 - 0:55</t>
+  </si>
+  <si>
+    <t>1:13 - 1:21</t>
+  </si>
+  <si>
+    <t>2:41 - 3:17</t>
+  </si>
+  <si>
+    <t>4:44 - 4:51</t>
+  </si>
+  <si>
+    <t>8:53 - 8:57</t>
+  </si>
+  <si>
+    <t>9:17 - 9:32</t>
+  </si>
+  <si>
+    <t>10:46 - 10:49</t>
+  </si>
+  <si>
+    <t>11:00 - 11:20</t>
+  </si>
+  <si>
+    <t>13:00 - 13:07</t>
+  </si>
+  <si>
+    <t>13:13 - 13:50</t>
+  </si>
+  <si>
+    <t>14:51 - 14:58</t>
+  </si>
+  <si>
+    <t>15:55 - 16:17</t>
+  </si>
+  <si>
+    <t>17:04 - 17:08</t>
+  </si>
+  <si>
+    <t>17:24 - 18:15</t>
+  </si>
+  <si>
+    <t>18:24 - 18:28</t>
+  </si>
+  <si>
+    <t>20:20 - 20:24</t>
+  </si>
+  <si>
+    <t>21:00 - 21:15</t>
+  </si>
+  <si>
+    <t>21:36 - 21:40</t>
+  </si>
+  <si>
+    <t>22:20 - 22:29</t>
+  </si>
+  <si>
+    <t>22:39 - 22:45</t>
+  </si>
+  <si>
+    <t>22:55 - 23:05</t>
+  </si>
+  <si>
+    <t>23:19 - 23:26</t>
+  </si>
+  <si>
+    <t>24:11 - 24:45</t>
+  </si>
+  <si>
+    <t>25:17 - 26:00</t>
+  </si>
+  <si>
+    <t>26:18 - 27:02</t>
+  </si>
+  <si>
+    <t>28:02 - 29:57</t>
+  </si>
+  <si>
+    <t>30:07 - 31:55</t>
+  </si>
+  <si>
+    <t>32:06 - 32:45</t>
+  </si>
+  <si>
+    <t>32:57 - 33:08</t>
+  </si>
+  <si>
+    <t>33:17 - 33:33</t>
+  </si>
+  <si>
+    <t>33:45 - 33:53</t>
+  </si>
+  <si>
+    <t>34:03 - 34:18</t>
+  </si>
+  <si>
+    <t>34:28 - 34:53</t>
+  </si>
+  <si>
+    <t>35:00 - 35:07</t>
+  </si>
+  <si>
+    <t>35:10 - 36:58</t>
+  </si>
+  <si>
+    <t>37:11 - 38:30</t>
+  </si>
+  <si>
+    <t>38:37 - 39:39</t>
+  </si>
+  <si>
+    <t>39:43 - 40:38</t>
+  </si>
+  <si>
+    <t>40:49 - 41:06</t>
+  </si>
+  <si>
+    <t>41:27 - 41:32</t>
+  </si>
+  <si>
+    <t>41:52 - 42:14</t>
+  </si>
+  <si>
+    <t>42:29 - 42:48</t>
+  </si>
+  <si>
+    <t>42:53 - 43:06</t>
+  </si>
+  <si>
+    <t>43:10 - 43:20</t>
+  </si>
+  <si>
+    <t>43:29 - 45:33</t>
+  </si>
+  <si>
+    <t>45:55 - 46:29</t>
+  </si>
+  <si>
+    <t>46:51 - 47:06</t>
+  </si>
+  <si>
+    <t>47:10 - 50:15</t>
+  </si>
+  <si>
+    <t>51:04 - 51:24</t>
+  </si>
+  <si>
+    <t>51:40 - 52:54</t>
+  </si>
+  <si>
+    <t>53:34 - 53:42</t>
+  </si>
+  <si>
+    <t>53:45 - 53:48</t>
+  </si>
+  <si>
+    <t>53:52 - 54:31</t>
+  </si>
+  <si>
+    <t>54:42 - 55:17</t>
+  </si>
+  <si>
+    <t>55:39 - 58:30</t>
+  </si>
+  <si>
+    <t>58:37 - 59:10</t>
+  </si>
+  <si>
+    <t>59:22 - 59:29</t>
+  </si>
+  <si>
+    <t>59:41 - 59:50</t>
+  </si>
+  <si>
+    <t>1:00:25 - 1:00:35</t>
+  </si>
+  <si>
+    <t>1:00:57 - 1:01:04</t>
+  </si>
+  <si>
+    <t>1:01:41 - 1:01:53</t>
+  </si>
+  <si>
+    <t>16:24 - 16:30</t>
+  </si>
+  <si>
+    <t>17:16 - 17:25</t>
+  </si>
+  <si>
+    <t>18:00 - 18:20</t>
+  </si>
+  <si>
+    <t>21:09 - 21:15</t>
+  </si>
+  <si>
+    <t>26:41 - 26:44</t>
+  </si>
+  <si>
+    <t>27:33 - 27:56</t>
+  </si>
+  <si>
+    <t>33:14 - 33:19</t>
+  </si>
+  <si>
+    <t>34:09 - 34:12</t>
+  </si>
+  <si>
+    <t>35:34 - 35:39</t>
+  </si>
+  <si>
+    <t>38:50 - 39:08</t>
+  </si>
+  <si>
+    <t>39:20 - 39:24</t>
+  </si>
+  <si>
+    <t>39:39 - 39:42</t>
+  </si>
+  <si>
+    <t>40:46 - 40:52</t>
+  </si>
+  <si>
+    <t>44:11 - 44:23</t>
+  </si>
+  <si>
+    <t>45:27 - 45:29</t>
+  </si>
+  <si>
+    <t>46:29 - 46:32</t>
+  </si>
+  <si>
+    <t>47:10 - 47:15</t>
+  </si>
+  <si>
+    <t>48:33 - 48:46</t>
+  </si>
+  <si>
+    <t>50:49 - 50:54</t>
+  </si>
+  <si>
+    <t>51:27 - 51:43</t>
+  </si>
+  <si>
+    <t>51:48 - 52:36</t>
+  </si>
+  <si>
+    <t>52:49 - 53:10</t>
+  </si>
+  <si>
+    <t>54:27 - 54:36</t>
+  </si>
+  <si>
+    <t>54:47 - 54:50</t>
+  </si>
+  <si>
+    <t>54:54 - 55:01</t>
+  </si>
+  <si>
+    <t>55:12 - 55:17</t>
+  </si>
+  <si>
+    <t>55:58 - 56:00</t>
+  </si>
+  <si>
+    <t>56:36 - 57:27</t>
+  </si>
+  <si>
+    <t>57:37 - 57:40</t>
+  </si>
+  <si>
+    <t>58:18 - 58:43</t>
+  </si>
+  <si>
+    <t>59:27 - 1:00:03</t>
+  </si>
+  <si>
+    <t>0:00 - 0:25</t>
+  </si>
+  <si>
+    <t>0:30 - 0:33</t>
+  </si>
+  <si>
+    <t>1:24 - 1:28</t>
+  </si>
+  <si>
+    <t>3:40 - 4:22</t>
+  </si>
+  <si>
+    <t>7:18 - 7:23</t>
+  </si>
+  <si>
+    <t>7:54 - 7:56</t>
+  </si>
+  <si>
+    <t>8:14 - 8:20</t>
+  </si>
+  <si>
+    <t>8:27 - 8:42</t>
+  </si>
+  <si>
+    <t>9:00 - 10:24</t>
+  </si>
+  <si>
+    <t>10:38 - 10:47</t>
+  </si>
+  <si>
+    <t>12:42 - 12:45</t>
+  </si>
+  <si>
+    <t>13:27 - 13:31</t>
+  </si>
+  <si>
+    <t>13:43 - 32:27</t>
+  </si>
+  <si>
+    <t>33:00 - 1:00:09</t>
+  </si>
+  <si>
+    <t>15:35 - 15:47</t>
+  </si>
+  <si>
+    <t>23:19 - 23:40</t>
+  </si>
+  <si>
+    <t>26:51 - 26:54</t>
+  </si>
+  <si>
+    <t>29:33 - 29:36</t>
+  </si>
+  <si>
+    <t>32:38 - 33:29</t>
+  </si>
+  <si>
+    <t>38:13 - 38:16</t>
+  </si>
+  <si>
+    <t>39:29 - 39:33</t>
+  </si>
+  <si>
+    <t>40:37 - 40:48</t>
+  </si>
+  <si>
+    <t>41:10 - 41:43</t>
+  </si>
+  <si>
+    <t>41:50 - 44:30</t>
+  </si>
+  <si>
+    <t>44:46 - 46:12</t>
+  </si>
+  <si>
+    <t>49:22 - 49:28</t>
+  </si>
+  <si>
+    <t>49:48 - 49:52</t>
+  </si>
+  <si>
+    <t>50:07 - 50:45</t>
+  </si>
+  <si>
+    <t>50:54 - 51:15</t>
+  </si>
+  <si>
+    <t>52:06 - 52:14</t>
+  </si>
+  <si>
+    <t>53:17 - 53:56</t>
+  </si>
+  <si>
+    <t>55:34 - 56:13</t>
+  </si>
+  <si>
+    <t>56:18 - 56:21</t>
+  </si>
+  <si>
+    <t>56:42 - 56:55</t>
+  </si>
+  <si>
+    <t>57:03 - 57:07</t>
+  </si>
+  <si>
+    <t>58:21 - 58:25</t>
+  </si>
+  <si>
+    <t>59:58 - 1:00:03</t>
+  </si>
+  <si>
+    <t>0:52 - 0:54</t>
+  </si>
+  <si>
+    <t>2:35 - 2:39</t>
+  </si>
+  <si>
+    <t>4:21 - 4:37</t>
+  </si>
+  <si>
+    <t>6:24 - 7:55</t>
+  </si>
+  <si>
+    <t>8:06 - 9:04</t>
+  </si>
+  <si>
+    <t>11:08 - 11:15</t>
+  </si>
+  <si>
+    <t>12:04 - 12:14</t>
+  </si>
+  <si>
+    <t>12:37 - 13:12</t>
+  </si>
+  <si>
+    <t>13:17 - 13:42</t>
+  </si>
+  <si>
+    <t>14:08 - 14:22</t>
+  </si>
+  <si>
+    <t>15:19 - 15:40</t>
+  </si>
+  <si>
+    <t>16:42 - 22:23</t>
+  </si>
+  <si>
+    <t>23:19 - 29:51</t>
+  </si>
+  <si>
+    <t>31:17 - 1:00:15</t>
+  </si>
+  <si>
     <t>0:04 - 0:08</t>
   </si>
   <si>
@@ -3147,9 +4075,6 @@
     <t>58:29 - 59:06</t>
   </si>
   <si>
-    <t>59:58 - 1:00:03</t>
-  </si>
-  <si>
     <t>1:00:14 - 1:00:22</t>
   </si>
   <si>
@@ -3300,9 +4225,6 @@
     <t>50:23 - 50:36</t>
   </si>
   <si>
-    <t>50:49 - 51:05</t>
-  </si>
-  <si>
     <t>51:11 - 51:13</t>
   </si>
   <si>
@@ -3613,6 +4535,426 @@
   </si>
   <si>
     <t>59:54 - 59:58</t>
+  </si>
+  <si>
+    <t>15:27 - 15:30</t>
+  </si>
+  <si>
+    <t>17:31 - 17:34</t>
+  </si>
+  <si>
+    <t>17:58 - 18:00</t>
+  </si>
+  <si>
+    <t>18:39 - 18:45</t>
+  </si>
+  <si>
+    <t>23:46 - 23:49</t>
+  </si>
+  <si>
+    <t>24:13 - 24:16</t>
+  </si>
+  <si>
+    <t>25:28 - 25:30</t>
+  </si>
+  <si>
+    <t>26:12 - 26:15</t>
+  </si>
+  <si>
+    <t>26:23 - 26:34</t>
+  </si>
+  <si>
+    <t>26:40 - 26:50</t>
+  </si>
+  <si>
+    <t>26:55 - 27:02</t>
+  </si>
+  <si>
+    <t>27:06 - 27:15</t>
+  </si>
+  <si>
+    <t>27:24 - 27:42</t>
+  </si>
+  <si>
+    <t>28:07 - 28:20</t>
+  </si>
+  <si>
+    <t>28:35 - 28:40</t>
+  </si>
+  <si>
+    <t>28:50 - 28:54</t>
+  </si>
+  <si>
+    <t>28:59 - 29:07</t>
+  </si>
+  <si>
+    <t>29:19 - 29:26</t>
+  </si>
+  <si>
+    <t>29:40 - 29:46</t>
+  </si>
+  <si>
+    <t>30:20 - 30:30</t>
+  </si>
+  <si>
+    <t>30:42 - 30:46</t>
+  </si>
+  <si>
+    <t>30:59 - 31:01</t>
+  </si>
+  <si>
+    <t>31:09 - 31:12</t>
+  </si>
+  <si>
+    <t>31:30 - 31:36</t>
+  </si>
+  <si>
+    <t>32:18 - 32:24</t>
+  </si>
+  <si>
+    <t>33:57 - 34:00</t>
+  </si>
+  <si>
+    <t>34:39 - 34:41</t>
+  </si>
+  <si>
+    <t>34:49 - 34:51</t>
+  </si>
+  <si>
+    <t>35:06 - 35:08</t>
+  </si>
+  <si>
+    <t>35:23 - 35:27</t>
+  </si>
+  <si>
+    <t>35:41 - 35:45</t>
+  </si>
+  <si>
+    <t>36:20 - 36:23</t>
+  </si>
+  <si>
+    <t>36:40 - 36:42</t>
+  </si>
+  <si>
+    <t>38:03 - 38:12</t>
+  </si>
+  <si>
+    <t>38:28 - 38:40</t>
+  </si>
+  <si>
+    <t>38:43 - 38:47</t>
+  </si>
+  <si>
+    <t>40:55 - 41:00</t>
+  </si>
+  <si>
+    <t>41:24 - 41:34</t>
+  </si>
+  <si>
+    <t>42:03 - 42:05</t>
+  </si>
+  <si>
+    <t>42:13 - 42:17</t>
+  </si>
+  <si>
+    <t>42:38 - 42:45</t>
+  </si>
+  <si>
+    <t>43:31 - 43:34</t>
+  </si>
+  <si>
+    <t>43:50 - 43:58</t>
+  </si>
+  <si>
+    <t>44:27 - 44:36</t>
+  </si>
+  <si>
+    <t>44:57 - 45:00</t>
+  </si>
+  <si>
+    <t>45:11 - 45:24</t>
+  </si>
+  <si>
+    <t>45:43 - 45:50</t>
+  </si>
+  <si>
+    <t>45:58 - 46:00</t>
+  </si>
+  <si>
+    <t>47:11 - 47:16</t>
+  </si>
+  <si>
+    <t>47:26 - 47:29</t>
+  </si>
+  <si>
+    <t>49:08 - 49:11</t>
+  </si>
+  <si>
+    <t>49:32 - 49:36</t>
+  </si>
+  <si>
+    <t>50:00 - 50:05</t>
+  </si>
+  <si>
+    <t>50:39 - 50:47</t>
+  </si>
+  <si>
+    <t>50:54 - 50:56</t>
+  </si>
+  <si>
+    <t>52:59 - 53:03</t>
+  </si>
+  <si>
+    <t>53:23 - 53:30</t>
+  </si>
+  <si>
+    <t>54:48 - 54:50</t>
+  </si>
+  <si>
+    <t>56:25 - 56:28</t>
+  </si>
+  <si>
+    <t>58:33 - 59:01</t>
+  </si>
+  <si>
+    <t>59:57 - 59:59</t>
+  </si>
+  <si>
+    <t>3:21 - 3:23</t>
+  </si>
+  <si>
+    <t>8:51 - 9:14</t>
+  </si>
+  <si>
+    <t>16:02 - 16:22</t>
+  </si>
+  <si>
+    <t>16:37 - 16:40</t>
+  </si>
+  <si>
+    <t>16:51 - 17:00</t>
+  </si>
+  <si>
+    <t>17:13 - 17:33</t>
+  </si>
+  <si>
+    <t>19:07 - 19:10</t>
+  </si>
+  <si>
+    <t>19:30 - 19:33</t>
+  </si>
+  <si>
+    <t>21:24 - 21:26</t>
+  </si>
+  <si>
+    <t>21:38 - 21:40</t>
+  </si>
+  <si>
+    <t>22:52 - 22:55</t>
+  </si>
+  <si>
+    <t>24:43 - 24:45</t>
+  </si>
+  <si>
+    <t>26:10 - 26:16</t>
+  </si>
+  <si>
+    <t>27:42 - 27:45</t>
+  </si>
+  <si>
+    <t>27:50 - 27:54</t>
+  </si>
+  <si>
+    <t>28:27 - 28:29</t>
+  </si>
+  <si>
+    <t>29:28 - 29:30</t>
+  </si>
+  <si>
+    <t>30:35 - 30:37</t>
+  </si>
+  <si>
+    <t>31:04 - 31:07</t>
+  </si>
+  <si>
+    <t>32:06 - 32:08</t>
+  </si>
+  <si>
+    <t>32:11 - 32:14</t>
+  </si>
+  <si>
+    <t>32:42 - 32:46</t>
+  </si>
+  <si>
+    <t>33:46 - 33:48</t>
+  </si>
+  <si>
+    <t>33:53 - 33:55</t>
+  </si>
+  <si>
+    <t>34:30 - 34:32</t>
+  </si>
+  <si>
+    <t>35:11 - 35:25</t>
+  </si>
+  <si>
+    <t>35:34 - 35:37</t>
+  </si>
+  <si>
+    <t>35:50 - 35:52</t>
+  </si>
+  <si>
+    <t>37:22 - 37:26</t>
+  </si>
+  <si>
+    <t>39:19 - 39:21</t>
+  </si>
+  <si>
+    <t>40:01 - 40:19</t>
+  </si>
+  <si>
+    <t>40:32 - 40:34</t>
+  </si>
+  <si>
+    <t>41:37 - 42:04</t>
+  </si>
+  <si>
+    <t>42:12 - 42:16</t>
+  </si>
+  <si>
+    <t>42:22 - 43:18</t>
+  </si>
+  <si>
+    <t>43:22 - 43:33</t>
+  </si>
+  <si>
+    <t>43:40 - 43:43</t>
+  </si>
+  <si>
+    <t>43:49 - 43:51</t>
+  </si>
+  <si>
+    <t>48:17 - 49:37</t>
+  </si>
+  <si>
+    <t>49:47 - 49:50</t>
+  </si>
+  <si>
+    <t>50:03 - 50:10</t>
+  </si>
+  <si>
+    <t>54:21 - 54:24</t>
+  </si>
+  <si>
+    <t>56:54 - 56:57</t>
+  </si>
+  <si>
+    <t>57:23 - 57:57</t>
+  </si>
+  <si>
+    <t>58:09 - 58:14</t>
+  </si>
+  <si>
+    <t>58:28 - 58:34</t>
+  </si>
+  <si>
+    <t>58:47 - 58:49</t>
+  </si>
+  <si>
+    <t>59:02 - 59:06</t>
+  </si>
+  <si>
+    <t>59:25 - 59:33</t>
+  </si>
+  <si>
+    <t>59:51 - 59:53</t>
+  </si>
+  <si>
+    <t>21:55 - 22:09</t>
+  </si>
+  <si>
+    <t>26:43 - 26:45</t>
+  </si>
+  <si>
+    <t>28:55- 28:59</t>
+  </si>
+  <si>
+    <t>30:26 - 30:29</t>
+  </si>
+  <si>
+    <t>31:59 - 32:02</t>
+  </si>
+  <si>
+    <t>38:17 - 38:19</t>
+  </si>
+  <si>
+    <t>38:40 - 38:43</t>
+  </si>
+  <si>
+    <t>41:23 - 41:44</t>
+  </si>
+  <si>
+    <t>43:21 - 43:23</t>
+  </si>
+  <si>
+    <t>44:31 - 44:33</t>
+  </si>
+  <si>
+    <t>44:52 - 44:55</t>
+  </si>
+  <si>
+    <t>45:01 - 45:10</t>
+  </si>
+  <si>
+    <t>45:44 - 45:48</t>
+  </si>
+  <si>
+    <t>45:54 - 46:00</t>
+  </si>
+  <si>
+    <t>46:59 - 47:04</t>
+  </si>
+  <si>
+    <t>47:35 - 47:38</t>
+  </si>
+  <si>
+    <t>49:14 - 49:17</t>
+  </si>
+  <si>
+    <t>49:38 - 49:40</t>
+  </si>
+  <si>
+    <t>50:08 - 50:11</t>
+  </si>
+  <si>
+    <t>51:03 - 51:15</t>
+  </si>
+  <si>
+    <t>51:37 - 51:40</t>
+  </si>
+  <si>
+    <t>52:01 - 52:03</t>
+  </si>
+  <si>
+    <t>53:19 - 53:31</t>
+  </si>
+  <si>
+    <t>53:46 - 53:49</t>
+  </si>
+  <si>
+    <t>55:26 - 55:43</t>
+  </si>
+  <si>
+    <t>57:35 - 57:39</t>
+  </si>
+  <si>
+    <t>57:50 - 57:53</t>
+  </si>
+  <si>
+    <t>58:09 - 58:24</t>
+  </si>
+  <si>
+    <t>58:41 - 59:09</t>
   </si>
 </sst>
 </file>
@@ -3622,7 +4964,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m-d"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -3648,31 +4990,13 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <color rgb="FF222222"/>
-      <name val="&quot;Google Sans&quot;"/>
-    </font>
-    <font>
-      <b/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1E9F7"/>
-        <bgColor rgb="FFE1E9F7"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3681,7 +5005,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3709,10 +5033,9 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="46" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -3893,7 +5216,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing49.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing50.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing51.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing52.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -17398,6 +18737,46 @@
         <v>46058.0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="C3" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="C5" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="C6" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="C7" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -17409,7 +18788,307 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C21" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C22" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C23" s="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C28" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -17422,7 +19101,247 @@
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11"/>
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C3" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C5" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C15" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C16" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C19" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C20" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C21" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C22" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C23" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C25" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C26" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C27" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C28" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C30" s="7">
+        <v>46058.0</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -17435,7 +19354,355 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C18" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C21" s="7">
+        <v>46027.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C31" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C43" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -17446,7 +19713,163 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C9" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C11" s="7">
+        <v>46086.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C12" s="7">
+        <v>46086.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C14" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C15" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C18" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C19" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -17457,7 +19880,291 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -20629,9 +23336,516 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="15.22"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12"/>
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C28" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C33" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C40" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C41" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C42" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C43" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C44" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C45" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C46" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C47" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C48" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C49" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C50" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C51" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C52" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C53" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C54" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C55" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C56" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C57" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C58" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C59" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C60" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C61" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C62" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C63" s="7">
+        <v>46056.0</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -20644,7 +23858,275 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C33" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -20655,7 +24137,134 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <sheetData/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="13.22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C5" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C14" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C15" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -20666,7 +24275,206 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <sheetData/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="13.89"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C6" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C11" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C12" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C13" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C15" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C16" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C19" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -20677,7 +24485,131 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C5" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C6" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C11" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C13" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C14" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C15" s="7">
+        <v>46027.0</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -20705,7 +24637,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>989</v>
+        <v>1297</v>
       </c>
       <c r="C2" s="1">
         <v>2.0</v>
@@ -20713,7 +24645,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>990</v>
+        <v>1298</v>
       </c>
       <c r="C3" s="7">
         <v>46024.0</v>
@@ -20721,7 +24653,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>991</v>
+        <v>1299</v>
       </c>
       <c r="C4" s="1">
         <v>2.0</v>
@@ -20729,7 +24661,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>992</v>
+        <v>1300</v>
       </c>
       <c r="C5" s="1">
         <v>2.0</v>
@@ -20737,7 +24669,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>993</v>
+        <v>1301</v>
       </c>
       <c r="C6" s="1">
         <v>2.0</v>
@@ -20745,7 +24677,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>994</v>
+        <v>1302</v>
       </c>
       <c r="C7" s="1">
         <v>2.0</v>
@@ -20753,7 +24685,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>995</v>
+        <v>1303</v>
       </c>
       <c r="C8" s="1">
         <v>2.0</v>
@@ -20761,7 +24693,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>996</v>
+        <v>1304</v>
       </c>
       <c r="C9" s="1">
         <v>2.0</v>
@@ -20769,7 +24701,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>997</v>
+        <v>1305</v>
       </c>
       <c r="C10" s="1">
         <v>2.0</v>
@@ -20777,7 +24709,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>998</v>
+        <v>1306</v>
       </c>
       <c r="C11" s="1">
         <v>2.0</v>
@@ -20785,7 +24717,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>999</v>
+        <v>1307</v>
       </c>
       <c r="C12" s="1">
         <v>2.0</v>
@@ -20793,7 +24725,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>1000</v>
+        <v>1308</v>
       </c>
       <c r="C13" s="1">
         <v>2.0</v>
@@ -20801,7 +24733,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>1001</v>
+        <v>1309</v>
       </c>
       <c r="C14" s="1">
         <v>2.0</v>
@@ -20809,7 +24741,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>1002</v>
+        <v>1310</v>
       </c>
       <c r="C15" s="1">
         <v>2.0</v>
@@ -20817,7 +24749,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>1003</v>
+        <v>1311</v>
       </c>
       <c r="C16" s="1">
         <v>2.0</v>
@@ -20825,7 +24757,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>1004</v>
+        <v>1312</v>
       </c>
       <c r="C17" s="1">
         <v>2.0</v>
@@ -20833,7 +24765,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>1005</v>
+        <v>1313</v>
       </c>
       <c r="C18" s="7">
         <v>46024.0</v>
@@ -20841,7 +24773,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>1006</v>
+        <v>1314</v>
       </c>
       <c r="C19" s="1">
         <v>2.0</v>
@@ -20849,7 +24781,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>1007</v>
+        <v>1315</v>
       </c>
       <c r="C20" s="1">
         <v>2.0</v>
@@ -20857,7 +24789,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>1008</v>
+        <v>1316</v>
       </c>
       <c r="C21" s="1">
         <v>2.0</v>
@@ -20865,7 +24797,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>1009</v>
+        <v>1317</v>
       </c>
       <c r="C22" s="1">
         <v>2.0</v>
@@ -20873,7 +24805,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>1010</v>
+        <v>1318</v>
       </c>
       <c r="C23" s="7">
         <v>46058.0</v>
@@ -20881,7 +24813,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>1011</v>
+        <v>1319</v>
       </c>
       <c r="C24" s="1">
         <v>2.0</v>
@@ -20889,7 +24821,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>1012</v>
+        <v>1320</v>
       </c>
       <c r="C25" s="1">
         <v>2.0</v>
@@ -20897,7 +24829,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>1013</v>
+        <v>1321</v>
       </c>
       <c r="C26" s="1">
         <v>2.0</v>
@@ -20905,7 +24837,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>1014</v>
+        <v>1322</v>
       </c>
       <c r="C27" s="1">
         <v>2.0</v>
@@ -20913,7 +24845,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>1015</v>
+        <v>1323</v>
       </c>
       <c r="C28" s="1">
         <v>2.0</v>
@@ -20921,7 +24853,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>1016</v>
+        <v>1324</v>
       </c>
       <c r="C29" s="7">
         <v>46058.0</v>
@@ -20929,7 +24861,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>1017</v>
+        <v>1325</v>
       </c>
       <c r="C30" s="1">
         <v>2.0</v>
@@ -20937,7 +24869,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>1018</v>
+        <v>1326</v>
       </c>
       <c r="C31" s="1">
         <v>2.0</v>
@@ -20945,7 +24877,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>1019</v>
+        <v>1327</v>
       </c>
       <c r="C32" s="1">
         <v>2.0</v>
@@ -20953,7 +24885,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>1020</v>
+        <v>1328</v>
       </c>
       <c r="C33" s="1">
         <v>2.0</v>
@@ -20961,7 +24893,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>1021</v>
+        <v>1329</v>
       </c>
       <c r="C34" s="1">
         <v>2.0</v>
@@ -20969,7 +24901,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>1022</v>
+        <v>1330</v>
       </c>
       <c r="C35" s="1">
         <v>2.0</v>
@@ -20977,7 +24909,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>1023</v>
+        <v>1331</v>
       </c>
       <c r="C36" s="1">
         <v>2.0</v>
@@ -20985,7 +24917,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>1024</v>
+        <v>1332</v>
       </c>
       <c r="C37" s="1">
         <v>2.0</v>
@@ -20993,7 +24925,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>1025</v>
+        <v>1333</v>
       </c>
       <c r="C38" s="1">
         <v>2.0</v>
@@ -21001,7 +24933,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>1026</v>
+        <v>1334</v>
       </c>
       <c r="C39" s="1">
         <v>2.0</v>
@@ -21009,7 +24941,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>1027</v>
+        <v>1335</v>
       </c>
       <c r="C40" s="1">
         <v>2.0</v>
@@ -21017,7 +24949,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>1028</v>
+        <v>1336</v>
       </c>
       <c r="C41" s="1">
         <v>2.0</v>
@@ -21025,7 +24957,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>1029</v>
+        <v>1282</v>
       </c>
       <c r="C42" s="1">
         <v>2.0</v>
@@ -21033,7 +24965,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>1030</v>
+        <v>1337</v>
       </c>
       <c r="C43" s="1">
         <v>2.0</v>
@@ -21041,7 +24973,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>1031</v>
+        <v>1338</v>
       </c>
       <c r="C44" s="1">
         <v>2.0</v>
@@ -21049,7 +24981,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>1032</v>
+        <v>1339</v>
       </c>
       <c r="C45" s="1">
         <v>2.0</v>
@@ -21057,7 +24989,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>1033</v>
+        <v>1340</v>
       </c>
       <c r="C46" s="1">
         <v>2.0</v>
@@ -21091,7 +25023,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>1034</v>
+        <v>1341</v>
       </c>
       <c r="C2" s="1">
         <v>2.0</v>
@@ -21099,42 +25031,42 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>1035</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>1036</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>1037</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>1038</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>1039</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>1040</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>1041</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>1042</v>
+        <v>1349</v>
       </c>
       <c r="C10" s="7">
         <v>46058.0</v>
@@ -21142,7 +25074,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>1043</v>
+        <v>1350</v>
       </c>
       <c r="C11" s="7">
         <v>46056.0</v>
@@ -21150,7 +25082,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>1044</v>
+        <v>1351</v>
       </c>
       <c r="C12" s="1">
         <v>2.0</v>
@@ -21158,7 +25090,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>1045</v>
+        <v>1352</v>
       </c>
       <c r="C13" s="1">
         <v>2.0</v>
@@ -21166,7 +25098,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>1046</v>
+        <v>1353</v>
       </c>
       <c r="C14" s="1">
         <v>2.0</v>
@@ -21174,7 +25106,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>1047</v>
+        <v>1354</v>
       </c>
       <c r="C15" s="1">
         <v>2.0</v>
@@ -21182,7 +25114,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>1048</v>
+        <v>1355</v>
       </c>
       <c r="C16" s="7">
         <v>46024.0</v>
@@ -21190,7 +25122,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>1049</v>
+        <v>1356</v>
       </c>
       <c r="C17" s="7">
         <v>46024.0</v>
@@ -21198,7 +25130,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>1050</v>
+        <v>1357</v>
       </c>
       <c r="C18" s="1">
         <v>2.0</v>
@@ -21206,7 +25138,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>1051</v>
+        <v>1358</v>
       </c>
       <c r="C19" s="7">
         <v>46027.0</v>
@@ -21214,7 +25146,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>1052</v>
+        <v>1359</v>
       </c>
       <c r="C20" s="7">
         <v>46027.0</v>
@@ -21222,7 +25154,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>1053</v>
+        <v>1360</v>
       </c>
       <c r="C21" s="7">
         <v>46027.0</v>
@@ -21256,7 +25188,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>1054</v>
+        <v>1361</v>
       </c>
       <c r="C2" s="1">
         <v>2.0</v>
@@ -21264,7 +25196,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>1055</v>
+        <v>1362</v>
       </c>
       <c r="C3" s="1">
         <v>2.0</v>
@@ -21272,7 +25204,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>1056</v>
+        <v>1363</v>
       </c>
       <c r="C4" s="1">
         <v>2.0</v>
@@ -21280,7 +25212,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>1057</v>
+        <v>1364</v>
       </c>
       <c r="C5" s="1">
         <v>2.0</v>
@@ -21288,7 +25220,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>1058</v>
+        <v>1365</v>
       </c>
       <c r="C6" s="1">
         <v>2.0</v>
@@ -21296,7 +25228,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>1059</v>
+        <v>1366</v>
       </c>
       <c r="C7" s="1">
         <v>2.0</v>
@@ -21304,7 +25236,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>1060</v>
+        <v>1367</v>
       </c>
       <c r="C8" s="1">
         <v>2.0</v>
@@ -21312,7 +25244,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>1061</v>
+        <v>1368</v>
       </c>
       <c r="C9" s="1">
         <v>2.0</v>
@@ -21320,7 +25252,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>1062</v>
+        <v>1369</v>
       </c>
       <c r="C10" s="1">
         <v>2.0</v>
@@ -21328,7 +25260,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>1063</v>
+        <v>1370</v>
       </c>
       <c r="C11" s="1">
         <v>2.0</v>
@@ -21336,7 +25268,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>1064</v>
+        <v>1371</v>
       </c>
       <c r="C12" s="1">
         <v>2.0</v>
@@ -21344,7 +25276,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>1065</v>
+        <v>1372</v>
       </c>
       <c r="C13" s="1">
         <v>2.0</v>
@@ -21352,7 +25284,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>1066</v>
+        <v>1373</v>
       </c>
       <c r="C14" s="1">
         <v>2.0</v>
@@ -21360,7 +25292,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>1067</v>
+        <v>1374</v>
       </c>
       <c r="C15" s="1">
         <v>2.0</v>
@@ -21368,7 +25300,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>1068</v>
+        <v>1375</v>
       </c>
       <c r="C16" s="1">
         <v>2.0</v>
@@ -21376,7 +25308,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>1069</v>
+        <v>1376</v>
       </c>
       <c r="C17" s="7">
         <v>46056.0</v>
@@ -21384,7 +25316,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>1070</v>
+        <v>1377</v>
       </c>
       <c r="C18" s="1">
         <v>3.0</v>
@@ -21392,7 +25324,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>1071</v>
+        <v>1378</v>
       </c>
       <c r="C19" s="1">
         <v>2.0</v>
@@ -21400,7 +25332,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>1072</v>
+        <v>1379</v>
       </c>
       <c r="C20" s="7">
         <v>46056.0</v>
@@ -21408,7 +25340,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>1073</v>
+        <v>1380</v>
       </c>
       <c r="C21" s="1">
         <v>2.0</v>
@@ -21416,7 +25348,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>1074</v>
+        <v>1381</v>
       </c>
       <c r="C22" s="1">
         <v>2.0</v>
@@ -21424,7 +25356,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>1075</v>
+        <v>1382</v>
       </c>
       <c r="C23" s="1">
         <v>2.0</v>
@@ -21432,7 +25364,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>1076</v>
+        <v>1383</v>
       </c>
       <c r="C24" s="1">
         <v>2.0</v>
@@ -21440,7 +25372,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>1077</v>
+        <v>1384</v>
       </c>
       <c r="C25" s="7">
         <v>46056.0</v>
@@ -21448,7 +25380,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>1078</v>
+        <v>1385</v>
       </c>
       <c r="C26" s="1">
         <v>2.0</v>
@@ -21456,7 +25388,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>1079</v>
+        <v>1386</v>
       </c>
       <c r="C27" s="1">
         <v>2.0</v>
@@ -21464,7 +25396,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="C28" s="7">
         <v>46056.0</v>
@@ -21472,7 +25404,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>1081</v>
+        <v>1387</v>
       </c>
       <c r="C29" s="1">
         <v>2.0</v>
@@ -21480,7 +25412,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>1082</v>
+        <v>1388</v>
       </c>
       <c r="C30" s="1">
         <v>3.0</v>
@@ -21488,7 +25420,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>1083</v>
+        <v>1389</v>
       </c>
       <c r="C31" s="1">
         <v>2.0</v>
@@ -21496,7 +25428,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>1084</v>
+        <v>1390</v>
       </c>
       <c r="C32" s="1">
         <v>2.0</v>
@@ -21504,7 +25436,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>1085</v>
+        <v>1391</v>
       </c>
       <c r="C33" s="1">
         <v>2.0</v>
@@ -21512,7 +25444,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>1086</v>
+        <v>1392</v>
       </c>
       <c r="C34" s="1">
         <v>2.0</v>
@@ -21520,7 +25452,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>1087</v>
+        <v>1393</v>
       </c>
       <c r="C35" s="1">
         <v>2.0</v>
@@ -21528,7 +25460,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>1088</v>
+        <v>1394</v>
       </c>
       <c r="C36" s="1">
         <v>2.0</v>
@@ -21536,7 +25468,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>1089</v>
+        <v>1395</v>
       </c>
       <c r="C37" s="1">
         <v>2.0</v>
@@ -21544,7 +25476,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>1090</v>
+        <v>1396</v>
       </c>
       <c r="C38" s="1">
         <v>2.0</v>
@@ -21552,7 +25484,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>1091</v>
+        <v>1397</v>
       </c>
       <c r="C39" s="7">
         <v>46056.0</v>
@@ -21560,7 +25492,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>1092</v>
+        <v>1398</v>
       </c>
       <c r="C40" s="1">
         <v>2.0</v>
@@ -21568,7 +25500,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>1093</v>
+        <v>1399</v>
       </c>
       <c r="C41" s="1">
         <v>2.0</v>
@@ -21576,7 +25508,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>1094</v>
+        <v>1400</v>
       </c>
       <c r="C42" s="1">
         <v>2.0</v>
@@ -21592,7 +25524,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>1095</v>
+        <v>1401</v>
       </c>
       <c r="C44" s="1">
         <v>2.0</v>
@@ -21600,7 +25532,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>1096</v>
+        <v>1402</v>
       </c>
       <c r="C45" s="1">
         <v>2.0</v>
@@ -21608,7 +25540,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>1097</v>
+        <v>1403</v>
       </c>
       <c r="C46" s="1">
         <v>2.0</v>
@@ -21616,7 +25548,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>1098</v>
+        <v>1404</v>
       </c>
       <c r="C47" s="1">
         <v>2.0</v>
@@ -21624,7 +25556,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>1099</v>
+        <v>1405</v>
       </c>
       <c r="C48" s="1">
         <v>2.0</v>
@@ -21632,7 +25564,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>1100</v>
+        <v>1406</v>
       </c>
       <c r="C49" s="1">
         <v>2.0</v>
@@ -21640,7 +25572,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>1101</v>
+        <v>1407</v>
       </c>
       <c r="C50" s="1">
         <v>2.0</v>
@@ -21648,7 +25580,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>1102</v>
+        <v>1408</v>
       </c>
       <c r="C51" s="1">
         <v>2.0</v>
@@ -21656,7 +25588,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>1103</v>
+        <v>1409</v>
       </c>
       <c r="C52" s="1">
         <v>2.0</v>
@@ -21664,7 +25596,7 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>1104</v>
+        <v>1410</v>
       </c>
       <c r="C53" s="1">
         <v>2.0</v>
@@ -21672,7 +25604,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>1105</v>
+        <v>1411</v>
       </c>
       <c r="C54" s="1">
         <v>2.0</v>
@@ -21680,7 +25612,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>1106</v>
+        <v>1412</v>
       </c>
       <c r="C55" s="1">
         <v>2.0</v>
@@ -21688,7 +25620,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>1107</v>
+        <v>1413</v>
       </c>
       <c r="C56" s="1">
         <v>2.0</v>
@@ -21719,7 +25651,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>1108</v>
+        <v>1414</v>
       </c>
       <c r="C2" s="1">
         <v>2.0</v>
@@ -21727,7 +25659,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>1109</v>
+        <v>1415</v>
       </c>
       <c r="C3" s="1">
         <v>2.0</v>
@@ -21735,7 +25667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>1110</v>
+        <v>1416</v>
       </c>
       <c r="C4" s="1">
         <v>2.0</v>
@@ -21743,7 +25675,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>1111</v>
+        <v>1417</v>
       </c>
       <c r="C5" s="1">
         <v>2.0</v>
@@ -21751,7 +25683,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>1112</v>
+        <v>1418</v>
       </c>
       <c r="C6" s="1">
         <v>2.0</v>
@@ -21759,7 +25691,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>1113</v>
+        <v>1419</v>
       </c>
       <c r="C7" s="1">
         <v>2.0</v>
@@ -21767,7 +25699,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>1114</v>
+        <v>1420</v>
       </c>
       <c r="C8" s="1">
         <v>2.0</v>
@@ -21775,7 +25707,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>1115</v>
+        <v>1421</v>
       </c>
       <c r="C9" s="1">
         <v>2.0</v>
@@ -21783,7 +25715,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>1116</v>
+        <v>1422</v>
       </c>
       <c r="C10" s="1">
         <v>2.0</v>
@@ -21791,7 +25723,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>1117</v>
+        <v>1423</v>
       </c>
       <c r="C11" s="1">
         <v>2.0</v>
@@ -21799,7 +25731,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>1118</v>
+        <v>1424</v>
       </c>
       <c r="C12" s="1">
         <v>2.0</v>
@@ -21807,7 +25739,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>1119</v>
+        <v>1425</v>
       </c>
       <c r="C13" s="1">
         <v>2.0</v>
@@ -21815,7 +25747,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>1120</v>
+        <v>1426</v>
       </c>
       <c r="C14" s="1">
         <v>2.0</v>
@@ -21823,7 +25755,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>1121</v>
+        <v>1427</v>
       </c>
       <c r="C15" s="1">
         <v>2.0</v>
@@ -21831,7 +25763,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>1122</v>
+        <v>1428</v>
       </c>
       <c r="C16" s="1">
         <v>2.0</v>
@@ -21839,7 +25771,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>1123</v>
+        <v>1429</v>
       </c>
       <c r="C17" s="1">
         <v>2.0</v>
@@ -21847,7 +25779,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>1124</v>
+        <v>1430</v>
       </c>
       <c r="C18" s="1">
         <v>2.0</v>
@@ -21855,7 +25787,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>1125</v>
+        <v>1431</v>
       </c>
       <c r="C19" s="1">
         <v>2.0</v>
@@ -21863,7 +25795,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>1126</v>
+        <v>1432</v>
       </c>
       <c r="C20" s="7">
         <v>46024.0</v>
@@ -21871,7 +25803,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>1127</v>
+        <v>1433</v>
       </c>
       <c r="C21" s="7">
         <v>46024.0</v>
@@ -21879,7 +25811,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>1128</v>
+        <v>1434</v>
       </c>
       <c r="C22" s="7">
         <v>46025.0</v>
@@ -21887,7 +25819,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>1129</v>
+        <v>1435</v>
       </c>
       <c r="C23" s="7">
         <v>46024.0</v>
@@ -21903,7 +25835,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>1130</v>
+        <v>1436</v>
       </c>
       <c r="C25" s="1">
         <v>3.0</v>
@@ -21911,7 +25843,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>1131</v>
+        <v>1437</v>
       </c>
       <c r="C26" s="7">
         <v>46056.0</v>
@@ -21919,7 +25851,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>1132</v>
+        <v>1438</v>
       </c>
       <c r="C27" s="1">
         <v>2.0</v>
@@ -21927,7 +25859,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>1133</v>
+        <v>1439</v>
       </c>
       <c r="C28" s="7">
         <v>46056.0</v>
@@ -21935,7 +25867,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>1134</v>
+        <v>1440</v>
       </c>
       <c r="C29" s="1">
         <v>2.0</v>
@@ -21943,7 +25875,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>1135</v>
+        <v>1441</v>
       </c>
       <c r="C30" s="1">
         <v>2.0</v>
@@ -21951,7 +25883,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>1136</v>
+        <v>1442</v>
       </c>
       <c r="C31" s="7">
         <v>46056.0</v>
@@ -21959,7 +25891,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>1137</v>
+        <v>1443</v>
       </c>
       <c r="C32" s="1">
         <v>2.0</v>
@@ -21967,7 +25899,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>1138</v>
+        <v>1444</v>
       </c>
       <c r="C33" s="7">
         <v>46025.0</v>
@@ -21975,7 +25907,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>1139</v>
+        <v>1445</v>
       </c>
       <c r="C34" s="7">
         <v>46056.0</v>
@@ -21983,7 +25915,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>1140</v>
+        <v>1446</v>
       </c>
       <c r="C35" s="1">
         <v>3.0</v>
@@ -21991,7 +25923,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>1141</v>
+        <v>1447</v>
       </c>
       <c r="C36" s="1">
         <v>3.0</v>
@@ -21999,7 +25931,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>1142</v>
+        <v>1448</v>
       </c>
       <c r="C37" s="7">
         <v>46025.0</v>
@@ -22007,7 +25939,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>1143</v>
+        <v>1449</v>
       </c>
       <c r="C38" s="1">
         <v>3.0</v>
@@ -22015,7 +25947,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>1144</v>
+        <v>1450</v>
       </c>
       <c r="C39" s="1">
         <v>3.0</v>
@@ -22023,7 +25955,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>1145</v>
+        <v>1451</v>
       </c>
       <c r="C40" s="1">
         <v>2.0</v>
@@ -22031,7 +25963,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>1146</v>
+        <v>1452</v>
       </c>
       <c r="C41" s="1">
         <v>2.0</v>
@@ -22039,7 +25971,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>1147</v>
+        <v>1453</v>
       </c>
       <c r="C42" s="1">
         <v>2.0</v>
@@ -22047,7 +25979,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>1148</v>
+        <v>1454</v>
       </c>
       <c r="C43" s="1">
         <v>2.0</v>
@@ -22055,7 +25987,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>1149</v>
+        <v>1455</v>
       </c>
       <c r="C44" s="7">
         <v>46056.0</v>
@@ -22063,7 +25995,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>1150</v>
+        <v>1456</v>
       </c>
       <c r="C45" s="7">
         <v>46056.0</v>
@@ -22071,7 +26003,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>1151</v>
+        <v>1457</v>
       </c>
       <c r="C46" s="7">
         <v>46056.0</v>
@@ -22079,7 +26011,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>1152</v>
+        <v>1458</v>
       </c>
       <c r="C47" s="7">
         <v>46025.0</v>
@@ -22087,7 +26019,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>1153</v>
+        <v>1459</v>
       </c>
       <c r="C48" s="7">
         <v>46056.0</v>
@@ -22095,7 +26027,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>1154</v>
+        <v>1460</v>
       </c>
       <c r="C49" s="7">
         <v>46056.0</v>
@@ -22103,7 +26035,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>1155</v>
+        <v>1461</v>
       </c>
       <c r="C50" s="7">
         <v>46056.0</v>
@@ -22111,7 +26043,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>1156</v>
+        <v>1462</v>
       </c>
       <c r="C51" s="7">
         <v>46056.0</v>
@@ -22119,7 +26051,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>1157</v>
+        <v>1463</v>
       </c>
       <c r="C52" s="7">
         <v>46056.0</v>
@@ -22127,7 +26059,7 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>1158</v>
+        <v>1464</v>
       </c>
       <c r="C53" s="7">
         <v>46056.0</v>
@@ -22135,7 +26067,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>1159</v>
+        <v>1465</v>
       </c>
       <c r="C54" s="7">
         <v>46056.0</v>
@@ -22143,7 +26075,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>1160</v>
+        <v>1466</v>
       </c>
       <c r="C55" s="7">
         <v>46056.0</v>
@@ -22151,7 +26083,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>1161</v>
+        <v>1467</v>
       </c>
       <c r="C56" s="7">
         <v>46056.0</v>
@@ -22159,7 +26091,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>1162</v>
+        <v>1468</v>
       </c>
       <c r="C57" s="7">
         <v>46056.0</v>
@@ -22167,7 +26099,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>1163</v>
+        <v>1469</v>
       </c>
       <c r="C58" s="7">
         <v>46056.0</v>
@@ -22175,7 +26107,7 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>1164</v>
+        <v>1470</v>
       </c>
       <c r="C59" s="7">
         <v>46056.0</v>
@@ -22183,7 +26115,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>1165</v>
+        <v>1471</v>
       </c>
       <c r="C60" s="7">
         <v>46056.0</v>
@@ -22191,7 +26123,7 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>1166</v>
+        <v>1472</v>
       </c>
       <c r="C61" s="7">
         <v>46056.0</v>
@@ -22199,7 +26131,7 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>1167</v>
+        <v>1473</v>
       </c>
       <c r="C62" s="7">
         <v>46056.0</v>
@@ -22207,7 +26139,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>1168</v>
+        <v>1474</v>
       </c>
       <c r="C63" s="1">
         <v>2.0</v>
@@ -22215,7 +26147,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>1169</v>
+        <v>1475</v>
       </c>
       <c r="C64" s="1">
         <v>2.0</v>
@@ -22223,7 +26155,7 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>1170</v>
+        <v>1476</v>
       </c>
       <c r="C65" s="1">
         <v>2.0</v>
@@ -22231,7 +26163,7 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>1171</v>
+        <v>1477</v>
       </c>
       <c r="C66" s="1">
         <v>2.0</v>
@@ -22239,7 +26171,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>1172</v>
+        <v>1478</v>
       </c>
       <c r="C67" s="1">
         <v>2.0</v>
@@ -22247,7 +26179,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>1173</v>
+        <v>1479</v>
       </c>
       <c r="C68" s="1">
         <v>2.0</v>
@@ -22255,7 +26187,7 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>1174</v>
+        <v>1480</v>
       </c>
       <c r="C69" s="1">
         <v>2.0</v>
@@ -22263,7 +26195,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>1175</v>
+        <v>1481</v>
       </c>
       <c r="C70" s="1">
         <v>2.0</v>
@@ -22271,7 +26203,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>1176</v>
+        <v>1482</v>
       </c>
       <c r="C71" s="1">
         <v>2.0</v>
@@ -22279,7 +26211,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>1177</v>
+        <v>1483</v>
       </c>
       <c r="C72" s="1">
         <v>2.0</v>
@@ -22287,7 +26219,7 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>1178</v>
+        <v>1484</v>
       </c>
       <c r="C73" s="1">
         <v>2.0</v>
@@ -22295,7 +26227,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>1179</v>
+        <v>1485</v>
       </c>
       <c r="C74" s="1">
         <v>2.0</v>
@@ -22303,7 +26235,7 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>1180</v>
+        <v>1486</v>
       </c>
       <c r="C75" s="1">
         <v>3.0</v>
@@ -22311,7 +26243,7 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>1181</v>
+        <v>1487</v>
       </c>
       <c r="C76" s="1">
         <v>3.0</v>
@@ -22319,7 +26251,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>1182</v>
+        <v>1488</v>
       </c>
       <c r="C77" s="1">
         <v>3.0</v>
@@ -22335,7 +26267,7 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>1183</v>
+        <v>1489</v>
       </c>
       <c r="C79" s="1">
         <v>2.0</v>
@@ -22343,10 +26275,553 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>1184</v>
+        <v>1490</v>
       </c>
       <c r="C80" s="7">
         <v>46056.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C39" s="7">
+        <v>46024.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C40" s="7">
+        <v>46024.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C50" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C52" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C53" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C54" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C55" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C56" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C58" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C59" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C60" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C61" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C62" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C63" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C64" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C65" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
@@ -23659,6 +28134,758 @@
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C3" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C7" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C37" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C38" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C39" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C40" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C41" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C43" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C44" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C45" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C50" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C52" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C53" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C54" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C55" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C56" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="11"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/data/seizure_stage.xlsx
+++ b/data/seizure_stage.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="1631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="1657">
   <si>
     <t>Stage</t>
   </si>
@@ -4955,6 +4955,84 @@
   </si>
   <si>
     <t>58:41 - 59:09</t>
+  </si>
+  <si>
+    <t>2:09 - 2:17</t>
+  </si>
+  <si>
+    <t>25:18 - 25:28</t>
+  </si>
+  <si>
+    <t>28:13 - 28:39</t>
+  </si>
+  <si>
+    <t>31:40 - 31:42</t>
+  </si>
+  <si>
+    <t>33:04 - 33:23</t>
+  </si>
+  <si>
+    <t>34:36 - 34:38</t>
+  </si>
+  <si>
+    <t>36:21 - 36:24</t>
+  </si>
+  <si>
+    <t>37:59 - 38:35</t>
+  </si>
+  <si>
+    <t>38:56 - 38:58</t>
+  </si>
+  <si>
+    <t>41:59 - 42:02</t>
+  </si>
+  <si>
+    <t>42:30 - 42:32</t>
+  </si>
+  <si>
+    <t>43:15 - 44:19</t>
+  </si>
+  <si>
+    <t>45:02 - 45:15</t>
+  </si>
+  <si>
+    <t>47:47 - 47:52</t>
+  </si>
+  <si>
+    <t>48:17 - 48:19</t>
+  </si>
+  <si>
+    <t>48:33 - 48:35</t>
+  </si>
+  <si>
+    <t>49:26 - 49:33</t>
+  </si>
+  <si>
+    <t>50:23 - 50:25</t>
+  </si>
+  <si>
+    <t>50:36 - 50:42</t>
+  </si>
+  <si>
+    <t>51:01 - 51:09</t>
+  </si>
+  <si>
+    <t>52:51 - 53:58</t>
+  </si>
+  <si>
+    <t>57:07 - 57:14</t>
+  </si>
+  <si>
+    <t>57:52 - 57:56</t>
+  </si>
+  <si>
+    <t>58:35 - 58:39</t>
+  </si>
+  <si>
+    <t>58:50 - 59:39</t>
+  </si>
+  <si>
+    <t>1:00:30 - 1:00:35</t>
   </si>
 </sst>
 </file>
@@ -28873,6 +28951,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="14.67"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
@@ -28883,6 +28964,269 @@
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46024.0</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C3" s="7">
+        <v>46056.0</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C9" s="7">
+        <v>46058.0</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C14" s="7">
+        <v>46058.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C26" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C31" s="7">
+        <v>46056.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
